--- a/bos-onboarding/test/DBO_HLI_18_v2.xlsx
+++ b/bos-onboarding/test/DBO_HLI_18_v2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\SDIOTECS_IN_BLR_ANANTA\2F_FILES\HLI-18\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\build2auto\bos-tools\bos-onboarding\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E15B2D-DB8E-4D93-A2EC-AF4372751A6E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFB471C-902B-4914-B4E6-57D3B56B5557}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="locations" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="1019">
   <si>
     <t>dbo.section</t>
   </si>
@@ -2137,6 +2137,966 @@
   </si>
   <si>
     <t>HVAC/VAV_SD_CSP</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_216</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_216</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_216</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_216</t>
+  </si>
+  <si>
+    <t>zone_air_co2_concentration_sensor_216</t>
+  </si>
+  <si>
+    <t>zone_air_co2_concentration_setpoint_216</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_217</t>
+  </si>
+  <si>
+    <t>zone_air_temperature_sensor_217</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_217</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_217</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_217</t>
+  </si>
+  <si>
+    <t>zone_air_cooling_temperature_setpoint_217</t>
+  </si>
+  <si>
+    <t>zone_occupancy_status_217</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_220</t>
+  </si>
+  <si>
+    <t>zone_air_temperature_sensor_220</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_220</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_220</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_220</t>
+  </si>
+  <si>
+    <t>zone_air_cooling_temperature_setpoint_220</t>
+  </si>
+  <si>
+    <t>zone_occupancy_status_220</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_222</t>
+  </si>
+  <si>
+    <t>zone_air_temperature_sensor_222</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_222</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_222</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_222</t>
+  </si>
+  <si>
+    <t>zone_air_cooling_temperature_setpoint_222</t>
+  </si>
+  <si>
+    <t>zone_occupancy_status_222</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_225</t>
+  </si>
+  <si>
+    <t>zone_air_temperature_sensor_225</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_225</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_225</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_225</t>
+  </si>
+  <si>
+    <t>zone_air_cooling_temperature_setpoint_225</t>
+  </si>
+  <si>
+    <t>zone_occupancy_status_225</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_226</t>
+  </si>
+  <si>
+    <t>zone_air_temperature_sensor_226</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_226</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_226</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_226</t>
+  </si>
+  <si>
+    <t>zone_air_cooling_temperature_setpoint_226</t>
+  </si>
+  <si>
+    <t>zone_occupancy_status_226</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_227</t>
+  </si>
+  <si>
+    <t>zone_air_temperature_sensor_227</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_227</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_227</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_227</t>
+  </si>
+  <si>
+    <t>zone_air_cooling_temperature_setpoint_227</t>
+  </si>
+  <si>
+    <t>zone_occupancy_status_227</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_228</t>
+  </si>
+  <si>
+    <t>zone_air_temperature_sensor_228</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_228</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_228</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_228</t>
+  </si>
+  <si>
+    <t>zone_air_cooling_temperature_setpoint_228</t>
+  </si>
+  <si>
+    <t>zone_occupancy_status_228</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_229</t>
+  </si>
+  <si>
+    <t>zone_air_temperature_sensor_229</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_229</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_229</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_229</t>
+  </si>
+  <si>
+    <t>zone_air_cooling_temperature_setpoint_229</t>
+  </si>
+  <si>
+    <t>zone_occupancy_status_229</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_232</t>
+  </si>
+  <si>
+    <t>zone_air_temperature_sensor_232</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_232</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_232</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_232</t>
+  </si>
+  <si>
+    <t>zone_air_cooling_temperature_setpoint_232</t>
+  </si>
+  <si>
+    <t>zone_occupancy_status_232</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_233</t>
+  </si>
+  <si>
+    <t>zone_air_temperature_sensor_233</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_233</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_233</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_233</t>
+  </si>
+  <si>
+    <t>zone_air_cooling_temperature_setpoint_233</t>
+  </si>
+  <si>
+    <t>zone_occupancy_status_233</t>
+  </si>
+  <si>
+    <t>zone_air_temperature_sensor_221</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_221</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_221</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_221</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_221</t>
+  </si>
+  <si>
+    <t>zone_air_cooling_temperature_setpoint_221</t>
+  </si>
+  <si>
+    <t>zone_occupancy_status_221</t>
+  </si>
+  <si>
+    <t>zone_air_temperature_sensor_230</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_230</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_230</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_230</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_230</t>
+  </si>
+  <si>
+    <t>zone_air_cooling_temperature_setpoint_230</t>
+  </si>
+  <si>
+    <t>zone_occupancy_status_230</t>
+  </si>
+  <si>
+    <t>zone_air_temperature_sensor_231</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_231</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_231</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_231</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_231</t>
+  </si>
+  <si>
+    <t>zone_air_cooling_temperature_setpoint_231</t>
+  </si>
+  <si>
+    <t>zone_occupancy_status_231</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_223</t>
+  </si>
+  <si>
+    <t>zone_air_temperature_sensor_223</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_223</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_223</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_223</t>
+  </si>
+  <si>
+    <t>zone_air_co2_concentration_sensor_223</t>
+  </si>
+  <si>
+    <t>zone_air_co2_concentration_setpoint_223</t>
+  </si>
+  <si>
+    <t>zone_air_cooling_temperature_setpoint_223</t>
+  </si>
+  <si>
+    <t>zone_occupancy_status_223</t>
+  </si>
+  <si>
+    <t>supply_air_damper_percentage_command_224</t>
+  </si>
+  <si>
+    <t>zone_air_temperature_sensor_224</t>
+  </si>
+  <si>
+    <t>supply_air_cooling_flowrate_capacity_224</t>
+  </si>
+  <si>
+    <t>supply_air_ventilation_flowrate_requirement_224</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_sensor_224</t>
+  </si>
+  <si>
+    <t>zone_air_co2_concentration_sensor_224</t>
+  </si>
+  <si>
+    <t>zone_air_co2_concentration_setpoint_224</t>
+  </si>
+  <si>
+    <t>zone_air_cooling_temperature_setpoint_224</t>
+  </si>
+  <si>
+    <t>zone_occupancy_status_224</t>
+  </si>
+  <si>
+    <t>energy_accumulator_21</t>
+  </si>
+  <si>
+    <t>power_sensor_21</t>
+  </si>
+  <si>
+    <t>phase1_power_sensor_21</t>
+  </si>
+  <si>
+    <t>phase2_power_sensor_21</t>
+  </si>
+  <si>
+    <t>phase3_power_sensor_21</t>
+  </si>
+  <si>
+    <t>apparent_power_sensor_21</t>
+  </si>
+  <si>
+    <t>phase1_apparent_power_sensor_21</t>
+  </si>
+  <si>
+    <t>phase2_apparent_power_sensor_21</t>
+  </si>
+  <si>
+    <t>phase3_apparent_power_sensor_21</t>
+  </si>
+  <si>
+    <t>powerfactor_sensor_21</t>
+  </si>
+  <si>
+    <t>phase1_line_current_sensor_21</t>
+  </si>
+  <si>
+    <t>phase2_line_current_sensor_21</t>
+  </si>
+  <si>
+    <t>phase3_line_current_sensor_21</t>
+  </si>
+  <si>
+    <t>line_frequency_sensor_21</t>
+  </si>
+  <si>
+    <t>reactive_power_sensor_21</t>
+  </si>
+  <si>
+    <t>phase1_reactive_power_sensor_21</t>
+  </si>
+  <si>
+    <t>phase2_reactive_power_sensor_21</t>
+  </si>
+  <si>
+    <t>phase3_reactive_power_sensor_21</t>
+  </si>
+  <si>
+    <t>phase1_neutral_line_voltage_sensor_21</t>
+  </si>
+  <si>
+    <t>phase2_neutral_line_voltage_sensor_21</t>
+  </si>
+  <si>
+    <t>phase3_neutral_line_voltage_sensor_21</t>
+  </si>
+  <si>
+    <t>phase1_phase2_line_voltage_sensor_21</t>
+  </si>
+  <si>
+    <t>phase2_phase3_line_voltage_sensor_21</t>
+  </si>
+  <si>
+    <t>phase1_phase3_line_voltage_sensor_21</t>
+  </si>
+  <si>
+    <t>energy_accumulator_22</t>
+  </si>
+  <si>
+    <t>power_sensor_22</t>
+  </si>
+  <si>
+    <t>phase1_power_sensor_22</t>
+  </si>
+  <si>
+    <t>phase2_power_sensor_22</t>
+  </si>
+  <si>
+    <t>phase3_power_sensor_22</t>
+  </si>
+  <si>
+    <t>apparent_power_sensor_22</t>
+  </si>
+  <si>
+    <t>phase1_apparent_power_sensor_22</t>
+  </si>
+  <si>
+    <t>phase2_apparent_power_sensor_22</t>
+  </si>
+  <si>
+    <t>phase3_apparent_power_sensor_22</t>
+  </si>
+  <si>
+    <t>powerfactor_sensor_22</t>
+  </si>
+  <si>
+    <t>phase1_line_current_sensor_22</t>
+  </si>
+  <si>
+    <t>phase2_line_current_sensor_22</t>
+  </si>
+  <si>
+    <t>phase3_line_current_sensor_22</t>
+  </si>
+  <si>
+    <t>line_frequency_sensor_22</t>
+  </si>
+  <si>
+    <t>reactive_power_sensor_22</t>
+  </si>
+  <si>
+    <t>phase1_reactive_power_sensor_22</t>
+  </si>
+  <si>
+    <t>phase2_reactive_power_sensor_22</t>
+  </si>
+  <si>
+    <t>phase3_reactive_power_sensor_22</t>
+  </si>
+  <si>
+    <t>phase1_neutral_line_voltage_sensor_22</t>
+  </si>
+  <si>
+    <t>phase2_neutral_line_voltage_sensor_22</t>
+  </si>
+  <si>
+    <t>phase3_neutral_line_voltage_sensor_22</t>
+  </si>
+  <si>
+    <t>phase1_phase2_line_voltage_sensor_22</t>
+  </si>
+  <si>
+    <t>phase2_phase3_line_voltage_sensor_22</t>
+  </si>
+  <si>
+    <t>phase1_phase3_line_voltage_sensor_22</t>
+  </si>
+  <si>
+    <t>energy_accumulator_23</t>
+  </si>
+  <si>
+    <t>power_sensor_23</t>
+  </si>
+  <si>
+    <t>phase1_power_sensor_23</t>
+  </si>
+  <si>
+    <t>phase2_power_sensor_23</t>
+  </si>
+  <si>
+    <t>phase3_power_sensor_23</t>
+  </si>
+  <si>
+    <t>apparent_power_sensor_23</t>
+  </si>
+  <si>
+    <t>phase1_apparent_power_sensor_23</t>
+  </si>
+  <si>
+    <t>phase2_apparent_power_sensor_23</t>
+  </si>
+  <si>
+    <t>phase3_apparent_power_sensor_23</t>
+  </si>
+  <si>
+    <t>powerfactor_sensor_23</t>
+  </si>
+  <si>
+    <t>phase1_line_current_sensor_23</t>
+  </si>
+  <si>
+    <t>phase2_line_current_sensor_23</t>
+  </si>
+  <si>
+    <t>phase3_line_current_sensor_23</t>
+  </si>
+  <si>
+    <t>line_frequency_sensor_23</t>
+  </si>
+  <si>
+    <t>reactive_power_sensor_23</t>
+  </si>
+  <si>
+    <t>phase1_reactive_power_sensor_23</t>
+  </si>
+  <si>
+    <t>phase2_reactive_power_sensor_23</t>
+  </si>
+  <si>
+    <t>phase3_reactive_power_sensor_23</t>
+  </si>
+  <si>
+    <t>phase1_neutral_line_voltage_sensor_23</t>
+  </si>
+  <si>
+    <t>phase2_neutral_line_voltage_sensor_23</t>
+  </si>
+  <si>
+    <t>phase3_neutral_line_voltage_sensor_23</t>
+  </si>
+  <si>
+    <t>phase1_phase2_line_voltage_sensor_23</t>
+  </si>
+  <si>
+    <t>phase2_phase3_line_voltage_sensor_23</t>
+  </si>
+  <si>
+    <t>phase1_phase3_line_voltage_sensor_23</t>
+  </si>
+  <si>
+    <t>energy_accumulator_24</t>
+  </si>
+  <si>
+    <t>power_sensor_24</t>
+  </si>
+  <si>
+    <t>phase1_power_sensor_24</t>
+  </si>
+  <si>
+    <t>phase2_power_sensor_24</t>
+  </si>
+  <si>
+    <t>phase3_power_sensor_24</t>
+  </si>
+  <si>
+    <t>apparent_power_sensor_24</t>
+  </si>
+  <si>
+    <t>phase1_apparent_power_sensor_24</t>
+  </si>
+  <si>
+    <t>phase2_apparent_power_sensor_24</t>
+  </si>
+  <si>
+    <t>phase3_apparent_power_sensor_24</t>
+  </si>
+  <si>
+    <t>powerfactor_sensor_24</t>
+  </si>
+  <si>
+    <t>phase1_line_current_sensor_24</t>
+  </si>
+  <si>
+    <t>phase2_line_current_sensor_24</t>
+  </si>
+  <si>
+    <t>phase3_line_current_sensor_24</t>
+  </si>
+  <si>
+    <t>line_frequency_sensor_24</t>
+  </si>
+  <si>
+    <t>reactive_power_sensor_24</t>
+  </si>
+  <si>
+    <t>phase1_reactive_power_sensor_24</t>
+  </si>
+  <si>
+    <t>phase2_reactive_power_sensor_24</t>
+  </si>
+  <si>
+    <t>phase3_reactive_power_sensor_24</t>
+  </si>
+  <si>
+    <t>phase1_neutral_line_voltage_sensor_24</t>
+  </si>
+  <si>
+    <t>phase2_neutral_line_voltage_sensor_24</t>
+  </si>
+  <si>
+    <t>phase3_neutral_line_voltage_sensor_24</t>
+  </si>
+  <si>
+    <t>phase1_phase2_line_voltage_sensor_24</t>
+  </si>
+  <si>
+    <t>phase2_phase3_line_voltage_sensor_24</t>
+  </si>
+  <si>
+    <t>phase1_phase3_line_voltage_sensor_24</t>
+  </si>
+  <si>
+    <t>energy_accumulator_25</t>
+  </si>
+  <si>
+    <t>power_sensor_25</t>
+  </si>
+  <si>
+    <t>phase1_power_sensor_25</t>
+  </si>
+  <si>
+    <t>phase2_power_sensor_25</t>
+  </si>
+  <si>
+    <t>phase3_power_sensor_25</t>
+  </si>
+  <si>
+    <t>apparent_power_sensor_25</t>
+  </si>
+  <si>
+    <t>phase1_apparent_power_sensor_25</t>
+  </si>
+  <si>
+    <t>phase2_apparent_power_sensor_25</t>
+  </si>
+  <si>
+    <t>phase3_apparent_power_sensor_25</t>
+  </si>
+  <si>
+    <t>powerfactor_sensor_25</t>
+  </si>
+  <si>
+    <t>phase1_line_current_sensor_25</t>
+  </si>
+  <si>
+    <t>phase2_line_current_sensor_25</t>
+  </si>
+  <si>
+    <t>phase3_line_current_sensor_25</t>
+  </si>
+  <si>
+    <t>line_frequency_sensor_25</t>
+  </si>
+  <si>
+    <t>reactive_power_sensor_25</t>
+  </si>
+  <si>
+    <t>phase1_reactive_power_sensor_25</t>
+  </si>
+  <si>
+    <t>phase2_reactive_power_sensor_25</t>
+  </si>
+  <si>
+    <t>phase3_reactive_power_sensor_25</t>
+  </si>
+  <si>
+    <t>phase1_neutral_line_voltage_sensor_25</t>
+  </si>
+  <si>
+    <t>phase2_neutral_line_voltage_sensor_25</t>
+  </si>
+  <si>
+    <t>phase3_neutral_line_voltage_sensor_25</t>
+  </si>
+  <si>
+    <t>phase1_phase2_line_voltage_sensor_25</t>
+  </si>
+  <si>
+    <t>phase2_phase3_line_voltage_sensor_25</t>
+  </si>
+  <si>
+    <t>phase1_phase3_line_voltage_sensor_25</t>
+  </si>
+  <si>
+    <t>energy_accumulator_26</t>
+  </si>
+  <si>
+    <t>power_sensor_26</t>
+  </si>
+  <si>
+    <t>phase1_power_sensor_26</t>
+  </si>
+  <si>
+    <t>phase2_power_sensor_26</t>
+  </si>
+  <si>
+    <t>phase3_power_sensor_26</t>
+  </si>
+  <si>
+    <t>apparent_power_sensor_26</t>
+  </si>
+  <si>
+    <t>phase1_apparent_power_sensor_26</t>
+  </si>
+  <si>
+    <t>phase2_apparent_power_sensor_26</t>
+  </si>
+  <si>
+    <t>phase3_apparent_power_sensor_26</t>
+  </si>
+  <si>
+    <t>powerfactor_sensor_26</t>
+  </si>
+  <si>
+    <t>phase1_line_current_sensor_26</t>
+  </si>
+  <si>
+    <t>phase2_line_current_sensor_26</t>
+  </si>
+  <si>
+    <t>phase3_line_current_sensor_26</t>
+  </si>
+  <si>
+    <t>line_frequency_sensor_26</t>
+  </si>
+  <si>
+    <t>reactive_power_sensor_26</t>
+  </si>
+  <si>
+    <t>phase1_reactive_power_sensor_26</t>
+  </si>
+  <si>
+    <t>phase2_reactive_power_sensor_26</t>
+  </si>
+  <si>
+    <t>phase3_reactive_power_sensor_26</t>
+  </si>
+  <si>
+    <t>phase1_neutral_line_voltage_sensor_26</t>
+  </si>
+  <si>
+    <t>phase2_neutral_line_voltage_sensor_26</t>
+  </si>
+  <si>
+    <t>phase3_neutral_line_voltage_sensor_26</t>
+  </si>
+  <si>
+    <t>phase1_phase2_line_voltage_sensor_26</t>
+  </si>
+  <si>
+    <t>phase2_phase3_line_voltage_sensor_26</t>
+  </si>
+  <si>
+    <t>phase1_phase3_line_voltage_sensor_26</t>
+  </si>
+  <si>
+    <t>power_sensor_308</t>
+  </si>
+  <si>
+    <t>powerfactor_sensor_308</t>
+  </si>
+  <si>
+    <t>generator_energy_accumulator_308</t>
+  </si>
+  <si>
+    <t>electricalgrid_energy_accumulator_308</t>
+  </si>
+  <si>
+    <t>energy_accumulator_308</t>
+  </si>
+  <si>
+    <t>power_sensor_320</t>
+  </si>
+  <si>
+    <t>powerfactor_sensor_320</t>
+  </si>
+  <si>
+    <t>generator_energy_accumulator_320</t>
+  </si>
+  <si>
+    <t>electricalgrid_energy_accumulator_320</t>
+  </si>
+  <si>
+    <t>energy_accumulator_320</t>
+  </si>
+  <si>
+    <t>power_sensor_333</t>
+  </si>
+  <si>
+    <t>powerfactor_sensor_333</t>
+  </si>
+  <si>
+    <t>generator_energy_accumulator_333</t>
+  </si>
+  <si>
+    <t>electricalgrid_energy_accumulator_333</t>
+  </si>
+  <si>
+    <t>energy_accumulator_333</t>
+  </si>
+  <si>
+    <t>power_sensor_334</t>
+  </si>
+  <si>
+    <t>powerfactor_sensor_334</t>
+  </si>
+  <si>
+    <t>generator_energy_accumulator_334</t>
+  </si>
+  <si>
+    <t>electricalgrid_energy_accumulator_334</t>
+  </si>
+  <si>
+    <t>energy_accumulator_334</t>
+  </si>
+  <si>
+    <t>power_sensor_357</t>
+  </si>
+  <si>
+    <t>powerfactor_sensor_357</t>
+  </si>
+  <si>
+    <t>generator_energy_accumulator_357</t>
+  </si>
+  <si>
+    <t>electricalgrid_energy_accumulator_357</t>
+  </si>
+  <si>
+    <t>energy_accumulator_357</t>
+  </si>
+  <si>
+    <t>power_sensor_358</t>
+  </si>
+  <si>
+    <t>powerfactor_sensor_358</t>
+  </si>
+  <si>
+    <t>generator_energy_accumulator_358</t>
+  </si>
+  <si>
+    <t>electricalgrid_energy_accumulator_358</t>
+  </si>
+  <si>
+    <t>energy_accumulator_358</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_216</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_217</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_220</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_221</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_222</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_223</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_224</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_225</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_226</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_227</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_228</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_229</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_230</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_231</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_232</t>
+  </si>
+  <si>
+    <t>supply_air_flowrate_setpoint_233</t>
+  </si>
+  <si>
+    <t>percent: percent</t>
+  </si>
+  <si>
+    <t>cubic_feet_per_minute: cubic_feet_per_minute</t>
+  </si>
+  <si>
+    <t>parts_per_million: parts_per_million</t>
+  </si>
+  <si>
+    <t>degrees_celsius: degrees_celsius</t>
+  </si>
+  <si>
+    <t>kilowatt_hours: kilowatt_hours</t>
+  </si>
+  <si>
+    <t>kilowatts: kilowatts</t>
+  </si>
+  <si>
+    <t>kilovolt_amperes_apparent: kilovolt_amperes_apparent</t>
+  </si>
+  <si>
+    <t>no_units: no_units</t>
+  </si>
+  <si>
+    <t>amperes: amperes</t>
+  </si>
+  <si>
+    <t>frequency: frequency</t>
+  </si>
+  <si>
+    <t>kilovolt_amperes_reactive: kilovolt_amperes_reactive</t>
+  </si>
+  <si>
+    <t>volts: volts</t>
+  </si>
+  <si>
+    <t>vav-216</t>
+  </si>
+  <si>
+    <t>1=OCCUPIED 0=UNOCCUPIED</t>
+  </si>
+  <si>
+    <t>cc69dcf3-9f07-4827-9181-3157f5d64c41</t>
   </si>
 </sst>
 </file>
@@ -3913,7 +4873,9 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
+      <c r="L5" s="3" t="s">
+        <v>1018</v>
+      </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -3927,17 +4889,17 @@
       </c>
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
+      <c r="V5" s="4" t="s">
+        <v>372</v>
+      </c>
       <c r="W5" s="3" t="s">
-        <v>696</v>
+        <v>1016</v>
       </c>
       <c r="X5" s="4" t="s">
         <v>60</v>
       </c>
       <c r="Y5" s="4"/>
-      <c r="Z5" s="4">
-        <v>12348774778</v>
-      </c>
+      <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
@@ -37946,7 +38908,7 @@
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="46.36328125" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="37.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="46.36328125" customWidth="1"/>
     <col min="7" max="7" width="35.6328125" customWidth="1"/>
     <col min="8" max="8" width="19.08984375" customWidth="1"/>
@@ -37996,9 +38958,13 @@
       <c r="D2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H2" s="1"/>
       <c r="I2" s="3" t="s">
         <v>58</v>
@@ -38017,9 +38983,13 @@
       <c r="D3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H3" s="1"/>
       <c r="I3" s="3" t="s">
         <v>58</v>
@@ -38039,8 +39009,12 @@
         <v>70</v>
       </c>
       <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="F4" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H4" s="1"/>
       <c r="I4" s="3" t="s">
         <v>58</v>
@@ -38060,8 +39034,12 @@
         <v>70</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="F5" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="3" t="s">
         <v>58</v>
@@ -38081,8 +39059,12 @@
         <v>71</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="F6" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>1006</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="3" t="s">
         <v>58</v>
@@ -38102,8 +39084,12 @@
         <v>71</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="F7" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>1006</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="3" t="s">
         <v>58</v>
@@ -38123,8 +39109,12 @@
         <v>69</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="F8" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="3" t="s">
         <v>58</v>
@@ -38144,8 +39134,12 @@
         <v>73</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="F9" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="3" t="s">
         <v>58</v>
@@ -38165,8 +39159,12 @@
         <v>70</v>
       </c>
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="F10" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="3" t="s">
         <v>58</v>
@@ -38186,8 +39184,12 @@
         <v>70</v>
       </c>
       <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
+      <c r="F11" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H11" s="1"/>
       <c r="I11" s="3" t="s">
         <v>58</v>
@@ -38207,8 +39209,12 @@
         <v>70</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
+      <c r="F12" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H12" s="1"/>
       <c r="I12" s="3" t="s">
         <v>58</v>
@@ -38228,8 +39234,12 @@
         <v>73</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
+      <c r="F13" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H13" s="1"/>
       <c r="I13" s="3" t="s">
         <v>58</v>
@@ -38246,9 +39256,13 @@
         <v>77</v>
       </c>
       <c r="D14" s="9"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
+      <c r="E14" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G14" s="3"/>
       <c r="H14" s="1"/>
       <c r="I14" s="3" t="s">
         <v>58</v>
@@ -38268,8 +39282,12 @@
         <v>69</v>
       </c>
       <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
+      <c r="F15" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H15" s="1"/>
       <c r="I15" s="3" t="s">
         <v>58</v>
@@ -38289,8 +39307,12 @@
         <v>73</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+      <c r="F16" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H16" s="1"/>
       <c r="I16" s="3" t="s">
         <v>58</v>
@@ -38310,8 +39332,12 @@
         <v>70</v>
       </c>
       <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+      <c r="F17" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H17" s="1"/>
       <c r="I17" s="3" t="s">
         <v>58</v>
@@ -38331,8 +39357,12 @@
         <v>70</v>
       </c>
       <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
+      <c r="F18" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H18" s="1"/>
       <c r="I18" s="3" t="s">
         <v>58</v>
@@ -38352,8 +39382,12 @@
         <v>70</v>
       </c>
       <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
+      <c r="F19" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H19" s="1"/>
       <c r="I19" s="3" t="s">
         <v>58</v>
@@ -38373,8 +39407,12 @@
         <v>73</v>
       </c>
       <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
+      <c r="F20" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H20" s="1"/>
       <c r="I20" s="3" t="s">
         <v>58</v>
@@ -38391,9 +39429,13 @@
         <v>83</v>
       </c>
       <c r="D21" s="9"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
+      <c r="E21" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="G21" s="3"/>
       <c r="H21" s="1"/>
       <c r="I21" s="3" t="s">
         <v>58</v>
@@ -38413,8 +39455,12 @@
         <v>69</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
+      <c r="F22" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H22" s="1"/>
       <c r="I22" s="3" t="s">
         <v>58</v>
@@ -38434,8 +39480,12 @@
         <v>73</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
+      <c r="F23" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H23" s="1"/>
       <c r="I23" s="3" t="s">
         <v>58</v>
@@ -38455,8 +39505,12 @@
         <v>70</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
+      <c r="F24" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H24" s="1"/>
       <c r="I24" s="3" t="s">
         <v>58</v>
@@ -38476,8 +39530,12 @@
         <v>70</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
+      <c r="F25" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H25" s="1"/>
       <c r="I25" s="3" t="s">
         <v>58</v>
@@ -38497,8 +39555,12 @@
         <v>70</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
+      <c r="F26" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H26" s="1"/>
       <c r="I26" s="3" t="s">
         <v>58</v>
@@ -38518,8 +39580,12 @@
         <v>73</v>
       </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
+      <c r="F27" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H27" s="1"/>
       <c r="I27" s="3" t="s">
         <v>58</v>
@@ -38536,9 +39602,13 @@
         <v>100</v>
       </c>
       <c r="D28" s="9"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
+      <c r="E28" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="G28" s="3"/>
       <c r="H28" s="1"/>
       <c r="I28" s="3" t="s">
         <v>58</v>
@@ -38558,8 +39628,12 @@
         <v>69</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
+      <c r="F29" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H29" s="1"/>
       <c r="I29" s="3" t="s">
         <v>58</v>
@@ -38579,8 +39653,12 @@
         <v>73</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
+      <c r="F30" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H30" s="1"/>
       <c r="I30" s="3" t="s">
         <v>58</v>
@@ -38600,8 +39678,12 @@
         <v>70</v>
       </c>
       <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
+      <c r="F31" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H31" s="1"/>
       <c r="I31" s="3" t="s">
         <v>58</v>
@@ -38621,8 +39703,12 @@
         <v>70</v>
       </c>
       <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
+      <c r="F32" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H32" s="1"/>
       <c r="I32" s="3" t="s">
         <v>58</v>
@@ -38642,8 +39728,12 @@
         <v>70</v>
       </c>
       <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
+      <c r="F33" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H33" s="1"/>
       <c r="I33" s="3" t="s">
         <v>58</v>
@@ -38663,8 +39753,12 @@
         <v>73</v>
       </c>
       <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
+      <c r="F34" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H34" s="1"/>
       <c r="I34" s="3" t="s">
         <v>58</v>
@@ -38681,9 +39775,13 @@
         <v>123</v>
       </c>
       <c r="D35" s="9"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
+      <c r="E35" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="G35" s="3"/>
       <c r="H35" s="1"/>
       <c r="I35" s="3" t="s">
         <v>58</v>
@@ -38703,8 +39801,12 @@
         <v>69</v>
       </c>
       <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
+      <c r="F36" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H36" s="1"/>
       <c r="I36" s="3" t="s">
         <v>58</v>
@@ -38724,8 +39826,12 @@
         <v>73</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
+      <c r="F37" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H37" s="1"/>
       <c r="I37" s="3" t="s">
         <v>58</v>
@@ -38745,8 +39851,12 @@
         <v>70</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
+      <c r="F38" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H38" s="1"/>
       <c r="I38" s="3" t="s">
         <v>58</v>
@@ -38766,8 +39876,12 @@
         <v>70</v>
       </c>
       <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
+      <c r="F39" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H39" s="1"/>
       <c r="I39" s="3" t="s">
         <v>58</v>
@@ -38787,8 +39901,12 @@
         <v>70</v>
       </c>
       <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
+      <c r="F40" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H40" s="1"/>
       <c r="I40" s="3" t="s">
         <v>58</v>
@@ -38808,8 +39926,12 @@
         <v>73</v>
       </c>
       <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
+      <c r="F41" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H41" s="1"/>
       <c r="I41" s="3" t="s">
         <v>58</v>
@@ -38826,9 +39948,13 @@
         <v>130</v>
       </c>
       <c r="D42" s="9"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
+      <c r="E42" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="G42" s="3"/>
       <c r="H42" s="1"/>
       <c r="I42" s="3" t="s">
         <v>58</v>
@@ -38848,8 +39974,12 @@
         <v>69</v>
       </c>
       <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
+      <c r="F43" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H43" s="1"/>
       <c r="I43" s="3" t="s">
         <v>58</v>
@@ -38869,8 +39999,12 @@
         <v>73</v>
       </c>
       <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
+      <c r="F44" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H44" s="1"/>
       <c r="I44" s="3" t="s">
         <v>58</v>
@@ -38890,8 +40024,12 @@
         <v>70</v>
       </c>
       <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
+      <c r="F45" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H45" s="1"/>
       <c r="I45" s="3" t="s">
         <v>58</v>
@@ -38911,8 +40049,12 @@
         <v>70</v>
       </c>
       <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
+      <c r="F46" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H46" s="1"/>
       <c r="I46" s="3" t="s">
         <v>58</v>
@@ -38932,8 +40074,12 @@
         <v>70</v>
       </c>
       <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
+      <c r="F47" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H47" s="1"/>
       <c r="I47" s="3" t="s">
         <v>58</v>
@@ -38953,8 +40099,12 @@
         <v>73</v>
       </c>
       <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
+      <c r="F48" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H48" s="1"/>
       <c r="I48" s="3" t="s">
         <v>58</v>
@@ -38971,9 +40121,13 @@
         <v>136</v>
       </c>
       <c r="D49" s="9"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
+      <c r="E49" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="G49" s="3"/>
       <c r="H49" s="1"/>
       <c r="I49" s="3" t="s">
         <v>58</v>
@@ -38993,8 +40147,12 @@
         <v>69</v>
       </c>
       <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
+      <c r="F50" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H50" s="1"/>
       <c r="I50" s="3" t="s">
         <v>58</v>
@@ -39014,8 +40172,12 @@
         <v>73</v>
       </c>
       <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
+      <c r="F51" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H51" s="1"/>
       <c r="I51" s="3" t="s">
         <v>58</v>
@@ -39035,8 +40197,12 @@
         <v>70</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
+      <c r="F52" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H52" s="1"/>
       <c r="I52" s="3" t="s">
         <v>58</v>
@@ -39056,8 +40222,12 @@
         <v>70</v>
       </c>
       <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
+      <c r="F53" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H53" s="1"/>
       <c r="I53" s="3" t="s">
         <v>58</v>
@@ -39077,8 +40247,12 @@
         <v>70</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
+      <c r="F54" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H54" s="1"/>
       <c r="I54" s="3" t="s">
         <v>58</v>
@@ -39098,8 +40272,12 @@
         <v>73</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
+      <c r="F55" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H55" s="1"/>
       <c r="I55" s="3" t="s">
         <v>58</v>
@@ -39116,9 +40294,13 @@
         <v>143</v>
       </c>
       <c r="D56" s="9"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
+      <c r="E56" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="G56" s="3"/>
       <c r="H56" s="1"/>
       <c r="I56" s="3" t="s">
         <v>58</v>
@@ -39138,8 +40320,12 @@
         <v>69</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
+      <c r="F57" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H57" s="1"/>
       <c r="I57" s="3" t="s">
         <v>58</v>
@@ -39159,8 +40345,12 @@
         <v>73</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
+      <c r="F58" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H58" s="1"/>
       <c r="I58" s="3" t="s">
         <v>58</v>
@@ -39180,8 +40370,12 @@
         <v>70</v>
       </c>
       <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
+      <c r="F59" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H59" s="1"/>
       <c r="I59" s="3" t="s">
         <v>58</v>
@@ -39201,8 +40395,12 @@
         <v>70</v>
       </c>
       <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
+      <c r="F60" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H60" s="1"/>
       <c r="I60" s="3" t="s">
         <v>58</v>
@@ -39222,8 +40420,12 @@
         <v>70</v>
       </c>
       <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
+      <c r="F61" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H61" s="1"/>
       <c r="I61" s="3" t="s">
         <v>58</v>
@@ -39243,8 +40445,12 @@
         <v>73</v>
       </c>
       <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
+      <c r="F62" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H62" s="1"/>
       <c r="I62" s="3" t="s">
         <v>58</v>
@@ -39261,9 +40467,13 @@
         <v>150</v>
       </c>
       <c r="D63" s="9"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
+      <c r="E63" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="G63" s="3"/>
       <c r="H63" s="1"/>
       <c r="I63" s="3" t="s">
         <v>58</v>
@@ -39283,8 +40493,12 @@
         <v>69</v>
       </c>
       <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
+      <c r="F64" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H64" s="1"/>
       <c r="I64" s="3" t="s">
         <v>58</v>
@@ -39304,8 +40518,12 @@
         <v>73</v>
       </c>
       <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
+      <c r="F65" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H65" s="1"/>
       <c r="I65" s="3" t="s">
         <v>58</v>
@@ -39325,8 +40543,12 @@
         <v>70</v>
       </c>
       <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
+      <c r="F66" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H66" s="1"/>
       <c r="I66" s="3" t="s">
         <v>58</v>
@@ -39346,8 +40568,12 @@
         <v>70</v>
       </c>
       <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
+      <c r="F67" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H67" s="1"/>
       <c r="I67" s="3" t="s">
         <v>58</v>
@@ -39367,8 +40593,12 @@
         <v>70</v>
       </c>
       <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
+      <c r="F68" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H68" s="1"/>
       <c r="I68" s="3" t="s">
         <v>58</v>
@@ -39388,8 +40618,12 @@
         <v>73</v>
       </c>
       <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
+      <c r="F69" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H69" s="1"/>
       <c r="I69" s="3" t="s">
         <v>58</v>
@@ -39406,9 +40640,13 @@
         <v>171</v>
       </c>
       <c r="D70" s="9"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
+      <c r="E70" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="G70" s="3"/>
       <c r="H70" s="1"/>
       <c r="I70" s="3" t="s">
         <v>58</v>
@@ -39428,8 +40666,12 @@
         <v>69</v>
       </c>
       <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
+      <c r="F71" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H71" s="1"/>
       <c r="I71" s="3" t="s">
         <v>58</v>
@@ -39449,8 +40691,12 @@
         <v>73</v>
       </c>
       <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
+      <c r="F72" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H72" s="1"/>
       <c r="I72" s="3" t="s">
         <v>58</v>
@@ -39470,8 +40716,12 @@
         <v>70</v>
       </c>
       <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
+      <c r="F73" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H73" s="1"/>
       <c r="I73" s="3" t="s">
         <v>58</v>
@@ -39491,8 +40741,12 @@
         <v>70</v>
       </c>
       <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
+      <c r="F74" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H74" s="1"/>
       <c r="I74" s="3" t="s">
         <v>58</v>
@@ -39512,8 +40766,12 @@
         <v>70</v>
       </c>
       <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
+      <c r="F75" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H75" s="1"/>
       <c r="I75" s="3" t="s">
         <v>58</v>
@@ -39533,8 +40791,12 @@
         <v>73</v>
       </c>
       <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
+      <c r="F76" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H76" s="1"/>
       <c r="I76" s="3" t="s">
         <v>58</v>
@@ -39551,9 +40813,13 @@
         <v>177</v>
       </c>
       <c r="D77" s="9"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
+      <c r="E77" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="G77" s="3"/>
       <c r="H77" s="1"/>
       <c r="I77" s="3" t="s">
         <v>58</v>
@@ -39573,8 +40839,12 @@
         <v>73</v>
       </c>
       <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
+      <c r="F78" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H78" s="1"/>
       <c r="I78" s="3" t="s">
         <v>58</v>
@@ -39594,8 +40864,12 @@
         <v>69</v>
       </c>
       <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
+      <c r="F79" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H79" s="1"/>
       <c r="I79" s="3" t="s">
         <v>58</v>
@@ -39615,8 +40889,12 @@
         <v>70</v>
       </c>
       <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
+      <c r="F80" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H80" s="1"/>
       <c r="I80" s="3" t="s">
         <v>58</v>
@@ -39636,8 +40914,12 @@
         <v>70</v>
       </c>
       <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
+      <c r="F81" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H81" s="1"/>
       <c r="I81" s="3" t="s">
         <v>58</v>
@@ -39657,8 +40939,12 @@
         <v>70</v>
       </c>
       <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
+      <c r="F82" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H82" s="1"/>
       <c r="I82" s="3" t="s">
         <v>58</v>
@@ -39678,8 +40964,12 @@
         <v>73</v>
       </c>
       <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
+      <c r="F83" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H83" s="1"/>
       <c r="I83" s="3" t="s">
         <v>58</v>
@@ -39696,9 +40986,13 @@
         <v>93</v>
       </c>
       <c r="D84" s="9"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
+      <c r="E84" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="G84" s="3"/>
       <c r="H84" s="1"/>
       <c r="I84" s="3" t="s">
         <v>58</v>
@@ -39718,8 +41012,12 @@
         <v>73</v>
       </c>
       <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
+      <c r="F85" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H85" s="1"/>
       <c r="I85" s="3" t="s">
         <v>58</v>
@@ -39739,8 +41037,12 @@
         <v>69</v>
       </c>
       <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
+      <c r="F86" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H86" s="1"/>
       <c r="I86" s="3" t="s">
         <v>58</v>
@@ -39760,8 +41062,12 @@
         <v>70</v>
       </c>
       <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
+      <c r="F87" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H87" s="1"/>
       <c r="I87" s="3" t="s">
         <v>58</v>
@@ -39781,8 +41087,12 @@
         <v>70</v>
       </c>
       <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
+      <c r="F88" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H88" s="1"/>
       <c r="I88" s="3" t="s">
         <v>58</v>
@@ -39802,8 +41112,12 @@
         <v>70</v>
       </c>
       <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
+      <c r="F89" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H89" s="1"/>
       <c r="I89" s="3" t="s">
         <v>58</v>
@@ -39823,8 +41137,12 @@
         <v>73</v>
       </c>
       <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
+      <c r="F90" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H90" s="1"/>
       <c r="I90" s="3" t="s">
         <v>58</v>
@@ -39841,9 +41159,13 @@
         <v>157</v>
       </c>
       <c r="D91" s="9"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
+      <c r="E91" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="G91" s="3"/>
       <c r="H91" s="1"/>
       <c r="I91" s="3" t="s">
         <v>58</v>
@@ -39863,8 +41185,12 @@
         <v>73</v>
       </c>
       <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
+      <c r="F92" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H92" s="1"/>
       <c r="I92" s="3" t="s">
         <v>58</v>
@@ -39884,8 +41210,12 @@
         <v>69</v>
       </c>
       <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
+      <c r="F93" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H93" s="1"/>
       <c r="I93" s="3" t="s">
         <v>58</v>
@@ -39905,8 +41235,12 @@
         <v>70</v>
       </c>
       <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
+      <c r="F94" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H94" s="1"/>
       <c r="I94" s="3" t="s">
         <v>58</v>
@@ -39926,8 +41260,12 @@
         <v>70</v>
       </c>
       <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
+      <c r="F95" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H95" s="1"/>
       <c r="I95" s="3" t="s">
         <v>58</v>
@@ -39947,8 +41285,12 @@
         <v>70</v>
       </c>
       <c r="E96" s="1"/>
-      <c r="F96" s="1"/>
-      <c r="G96" s="1"/>
+      <c r="F96" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H96" s="1"/>
       <c r="I96" s="3" t="s">
         <v>58</v>
@@ -39968,8 +41310,12 @@
         <v>73</v>
       </c>
       <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
-      <c r="G97" s="1"/>
+      <c r="F97" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H97" s="1"/>
       <c r="I97" s="3" t="s">
         <v>58</v>
@@ -39986,9 +41332,13 @@
         <v>164</v>
       </c>
       <c r="D98" s="9"/>
-      <c r="E98" s="1"/>
-      <c r="F98" s="1"/>
-      <c r="G98" s="1"/>
+      <c r="E98" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="G98" s="3"/>
       <c r="H98" s="1"/>
       <c r="I98" s="3" t="s">
         <v>58</v>
@@ -40008,8 +41358,12 @@
         <v>69</v>
       </c>
       <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
+      <c r="F99" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H99" s="1"/>
       <c r="I99" s="3" t="s">
         <v>58</v>
@@ -40029,8 +41383,12 @@
         <v>73</v>
       </c>
       <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
+      <c r="F100" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H100" s="1"/>
       <c r="I100" s="3" t="s">
         <v>58</v>
@@ -40050,8 +41408,12 @@
         <v>70</v>
       </c>
       <c r="E101" s="1"/>
-      <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
+      <c r="F101" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H101" s="1"/>
       <c r="I101" s="3" t="s">
         <v>58</v>
@@ -40071,8 +41433,12 @@
         <v>70</v>
       </c>
       <c r="E102" s="1"/>
-      <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
+      <c r="F102" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H102" s="1"/>
       <c r="I102" s="3" t="s">
         <v>58</v>
@@ -40092,8 +41458,12 @@
         <v>70</v>
       </c>
       <c r="E103" s="1"/>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
+      <c r="F103" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H103" s="1"/>
       <c r="I103" s="3" t="s">
         <v>58</v>
@@ -40113,8 +41483,12 @@
         <v>71</v>
       </c>
       <c r="E104" s="1"/>
-      <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
+      <c r="F104" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>1006</v>
+      </c>
       <c r="H104" s="1"/>
       <c r="I104" s="3" t="s">
         <v>58</v>
@@ -40134,8 +41508,12 @@
         <v>71</v>
       </c>
       <c r="E105" s="1"/>
-      <c r="F105" s="1"/>
-      <c r="G105" s="1"/>
+      <c r="F105" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>1006</v>
+      </c>
       <c r="H105" s="1"/>
       <c r="I105" s="3" t="s">
         <v>58</v>
@@ -40155,8 +41533,12 @@
         <v>73</v>
       </c>
       <c r="E106" s="1"/>
-      <c r="F106" s="1"/>
-      <c r="G106" s="1"/>
+      <c r="F106" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H106" s="1"/>
       <c r="I106" s="3" t="s">
         <v>58</v>
@@ -40173,9 +41555,13 @@
         <v>110</v>
       </c>
       <c r="D107" s="9"/>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
-      <c r="G107" s="1"/>
+      <c r="E107" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="G107" s="3"/>
       <c r="H107" s="1"/>
       <c r="I107" s="3" t="s">
         <v>58</v>
@@ -40195,8 +41581,12 @@
         <v>69</v>
       </c>
       <c r="E108" s="1"/>
-      <c r="F108" s="1"/>
-      <c r="G108" s="1"/>
+      <c r="F108" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>1004</v>
+      </c>
       <c r="H108" s="1"/>
       <c r="I108" s="3" t="s">
         <v>58</v>
@@ -40216,8 +41606,12 @@
         <v>73</v>
       </c>
       <c r="E109" s="1"/>
-      <c r="F109" s="1"/>
-      <c r="G109" s="1"/>
+      <c r="F109" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H109" s="1"/>
       <c r="I109" s="3" t="s">
         <v>58</v>
@@ -40237,8 +41631,12 @@
         <v>70</v>
       </c>
       <c r="E110" s="1"/>
-      <c r="F110" s="1"/>
-      <c r="G110" s="1"/>
+      <c r="F110" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H110" s="1"/>
       <c r="I110" s="3" t="s">
         <v>58</v>
@@ -40258,8 +41656,12 @@
         <v>70</v>
       </c>
       <c r="E111" s="1"/>
-      <c r="F111" s="1"/>
-      <c r="G111" s="1"/>
+      <c r="F111" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H111" s="1"/>
       <c r="I111" s="3" t="s">
         <v>58</v>
@@ -40279,8 +41681,12 @@
         <v>70</v>
       </c>
       <c r="E112" s="1"/>
-      <c r="F112" s="1"/>
-      <c r="G112" s="1"/>
+      <c r="F112" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H112" s="1"/>
       <c r="I112" s="3" t="s">
         <v>58</v>
@@ -40300,8 +41706,12 @@
         <v>71</v>
       </c>
       <c r="E113" s="1"/>
-      <c r="F113" s="1"/>
-      <c r="G113" s="1"/>
+      <c r="F113" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>1006</v>
+      </c>
       <c r="H113" s="1"/>
       <c r="I113" s="3" t="s">
         <v>58</v>
@@ -40321,8 +41731,12 @@
         <v>71</v>
       </c>
       <c r="E114" s="1"/>
-      <c r="F114" s="1"/>
-      <c r="G114" s="1"/>
+      <c r="F114" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>1006</v>
+      </c>
       <c r="H114" s="1"/>
       <c r="I114" s="3" t="s">
         <v>58</v>
@@ -40342,8 +41756,12 @@
         <v>73</v>
       </c>
       <c r="E115" s="1"/>
-      <c r="F115" s="1"/>
-      <c r="G115" s="1"/>
+      <c r="F115" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="H115" s="1"/>
       <c r="I115" s="3" t="s">
         <v>58</v>
@@ -40360,9 +41778,13 @@
         <v>117</v>
       </c>
       <c r="D116" s="9"/>
-      <c r="E116" s="1"/>
-      <c r="F116" s="1"/>
-      <c r="G116" s="1"/>
+      <c r="E116" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="G116" s="3"/>
       <c r="H116" s="1"/>
       <c r="I116" s="3" t="s">
         <v>58</v>
@@ -40382,8 +41804,12 @@
         <v>361</v>
       </c>
       <c r="E117" s="1"/>
-      <c r="F117" s="1"/>
-      <c r="G117" s="1"/>
+      <c r="F117" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H117" s="1"/>
       <c r="I117" s="3" t="s">
         <v>58</v>
@@ -40403,8 +41829,12 @@
         <v>362</v>
       </c>
       <c r="E118" s="1"/>
-      <c r="F118" s="1"/>
-      <c r="G118" s="1"/>
+      <c r="F118" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H118" s="1"/>
       <c r="I118" s="3" t="s">
         <v>58</v>
@@ -40424,8 +41854,12 @@
         <v>362</v>
       </c>
       <c r="E119" s="1"/>
-      <c r="F119" s="1"/>
-      <c r="G119" s="1"/>
+      <c r="F119" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H119" s="1"/>
       <c r="I119" s="3" t="s">
         <v>58</v>
@@ -40445,8 +41879,12 @@
         <v>362</v>
       </c>
       <c r="E120" s="1"/>
-      <c r="F120" s="1"/>
-      <c r="G120" s="1"/>
+      <c r="F120" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H120" s="1"/>
       <c r="I120" s="3" t="s">
         <v>58</v>
@@ -40466,8 +41904,12 @@
         <v>363</v>
       </c>
       <c r="E121" s="1"/>
-      <c r="F121" s="1"/>
-      <c r="G121" s="1"/>
+      <c r="F121" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H121" s="1"/>
       <c r="I121" s="3" t="s">
         <v>58</v>
@@ -40487,8 +41929,12 @@
         <v>363</v>
       </c>
       <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
+      <c r="F122" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H122" s="1"/>
       <c r="I122" s="3" t="s">
         <v>58</v>
@@ -40508,8 +41954,12 @@
         <v>363</v>
       </c>
       <c r="E123" s="1"/>
-      <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
+      <c r="F123" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H123" s="1"/>
       <c r="I123" s="3" t="s">
         <v>58</v>
@@ -40529,8 +41979,12 @@
         <v>363</v>
       </c>
       <c r="E124" s="1"/>
-      <c r="F124" s="1"/>
-      <c r="G124" s="1"/>
+      <c r="F124" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H124" s="1"/>
       <c r="I124" s="3" t="s">
         <v>58</v>
@@ -40550,8 +42004,12 @@
         <v>363</v>
       </c>
       <c r="E125" s="1"/>
-      <c r="F125" s="1"/>
-      <c r="G125" s="1"/>
+      <c r="F125" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H125" s="1"/>
       <c r="I125" s="3" t="s">
         <v>58</v>
@@ -40571,8 +42029,12 @@
         <v>364</v>
       </c>
       <c r="E126" s="1"/>
-      <c r="F126" s="1"/>
-      <c r="G126" s="1"/>
+      <c r="F126" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>1011</v>
+      </c>
       <c r="H126" s="1"/>
       <c r="I126" s="3" t="s">
         <v>58</v>
@@ -40592,8 +42054,12 @@
         <v>365</v>
       </c>
       <c r="E127" s="1"/>
-      <c r="F127" s="1"/>
-      <c r="G127" s="1"/>
+      <c r="F127" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H127" s="1"/>
       <c r="I127" s="3" t="s">
         <v>58</v>
@@ -40613,8 +42079,12 @@
         <v>365</v>
       </c>
       <c r="E128" s="1"/>
-      <c r="F128" s="1"/>
-      <c r="G128" s="1"/>
+      <c r="F128" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H128" s="1"/>
       <c r="I128" s="3" t="s">
         <v>58</v>
@@ -40634,8 +42104,12 @@
         <v>365</v>
       </c>
       <c r="E129" s="1"/>
-      <c r="F129" s="1"/>
-      <c r="G129" s="1"/>
+      <c r="F129" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H129" s="1"/>
       <c r="I129" s="3" t="s">
         <v>58</v>
@@ -40655,8 +42129,12 @@
         <v>366</v>
       </c>
       <c r="E130" s="1"/>
-      <c r="F130" s="1"/>
-      <c r="G130" s="1"/>
+      <c r="F130" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>1013</v>
+      </c>
       <c r="H130" s="1"/>
       <c r="I130" s="3" t="s">
         <v>58</v>
@@ -40676,8 +42154,12 @@
         <v>367</v>
       </c>
       <c r="E131" s="1"/>
-      <c r="F131" s="1"/>
-      <c r="G131" s="1"/>
+      <c r="F131" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H131" s="1"/>
       <c r="I131" s="3" t="s">
         <v>58</v>
@@ -40697,8 +42179,12 @@
         <v>367</v>
       </c>
       <c r="E132" s="1"/>
-      <c r="F132" s="1"/>
-      <c r="G132" s="1"/>
+      <c r="F132" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H132" s="1"/>
       <c r="I132" s="3" t="s">
         <v>58</v>
@@ -40718,8 +42204,12 @@
         <v>367</v>
       </c>
       <c r="E133" s="1"/>
-      <c r="F133" s="1"/>
-      <c r="G133" s="1"/>
+      <c r="F133" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H133" s="1"/>
       <c r="I133" s="3" t="s">
         <v>58</v>
@@ -40739,8 +42229,12 @@
         <v>367</v>
       </c>
       <c r="E134" s="1"/>
-      <c r="F134" s="1"/>
-      <c r="G134" s="1"/>
+      <c r="F134" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H134" s="1"/>
       <c r="I134" s="3" t="s">
         <v>58</v>
@@ -40760,8 +42254,12 @@
         <v>368</v>
       </c>
       <c r="E135" s="1"/>
-      <c r="F135" s="1"/>
-      <c r="G135" s="1"/>
+      <c r="F135" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H135" s="1"/>
       <c r="I135" s="3" t="s">
         <v>58</v>
@@ -40781,8 +42279,12 @@
         <v>368</v>
       </c>
       <c r="E136" s="1"/>
-      <c r="F136" s="1"/>
-      <c r="G136" s="1"/>
+      <c r="F136" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H136" s="1"/>
       <c r="I136" s="3" t="s">
         <v>58</v>
@@ -40802,8 +42304,12 @@
         <v>368</v>
       </c>
       <c r="E137" s="1"/>
-      <c r="F137" s="1"/>
-      <c r="G137" s="1"/>
+      <c r="F137" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H137" s="1"/>
       <c r="I137" s="3" t="s">
         <v>58</v>
@@ -40823,8 +42329,12 @@
         <v>368</v>
       </c>
       <c r="E138" s="1"/>
-      <c r="F138" s="1"/>
-      <c r="G138" s="1"/>
+      <c r="F138" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H138" s="1"/>
       <c r="I138" s="3" t="s">
         <v>58</v>
@@ -40844,8 +42354,12 @@
         <v>368</v>
       </c>
       <c r="E139" s="1"/>
-      <c r="F139" s="1"/>
-      <c r="G139" s="1"/>
+      <c r="F139" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H139" s="1"/>
       <c r="I139" s="3" t="s">
         <v>58</v>
@@ -40865,8 +42379,12 @@
         <v>368</v>
       </c>
       <c r="E140" s="1"/>
-      <c r="F140" s="1"/>
-      <c r="G140" s="1"/>
+      <c r="F140" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H140" s="1"/>
       <c r="I140" s="3" t="s">
         <v>58</v>
@@ -40886,8 +42404,12 @@
         <v>361</v>
       </c>
       <c r="E141" s="1"/>
-      <c r="F141" s="1"/>
-      <c r="G141" s="1"/>
+      <c r="F141" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H141" s="1"/>
       <c r="I141" s="3" t="s">
         <v>58</v>
@@ -40907,8 +42429,12 @@
         <v>362</v>
       </c>
       <c r="E142" s="1"/>
-      <c r="F142" s="1"/>
-      <c r="G142" s="1"/>
+      <c r="F142" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H142" s="1"/>
       <c r="I142" s="3" t="s">
         <v>58</v>
@@ -40928,8 +42454,12 @@
         <v>362</v>
       </c>
       <c r="E143" s="1"/>
-      <c r="F143" s="1"/>
-      <c r="G143" s="1"/>
+      <c r="F143" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H143" s="1"/>
       <c r="I143" s="3" t="s">
         <v>58</v>
@@ -40949,8 +42479,12 @@
         <v>362</v>
       </c>
       <c r="E144" s="1"/>
-      <c r="F144" s="1"/>
-      <c r="G144" s="1"/>
+      <c r="F144" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H144" s="1"/>
       <c r="I144" s="3" t="s">
         <v>58</v>
@@ -40970,8 +42504,12 @@
         <v>363</v>
       </c>
       <c r="E145" s="1"/>
-      <c r="F145" s="1"/>
-      <c r="G145" s="1"/>
+      <c r="F145" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H145" s="1"/>
       <c r="I145" s="3" t="s">
         <v>58</v>
@@ -40991,8 +42529,12 @@
         <v>363</v>
       </c>
       <c r="E146" s="1"/>
-      <c r="F146" s="1"/>
-      <c r="G146" s="1"/>
+      <c r="F146" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H146" s="1"/>
       <c r="I146" s="3" t="s">
         <v>58</v>
@@ -41012,8 +42554,12 @@
         <v>363</v>
       </c>
       <c r="E147" s="1"/>
-      <c r="F147" s="1"/>
-      <c r="G147" s="1"/>
+      <c r="F147" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H147" s="1"/>
       <c r="I147" s="3" t="s">
         <v>58</v>
@@ -41033,8 +42579,12 @@
         <v>363</v>
       </c>
       <c r="E148" s="1"/>
-      <c r="F148" s="1"/>
-      <c r="G148" s="1"/>
+      <c r="F148" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H148" s="1"/>
       <c r="I148" s="3" t="s">
         <v>58</v>
@@ -41054,8 +42604,12 @@
         <v>363</v>
       </c>
       <c r="E149" s="1"/>
-      <c r="F149" s="1"/>
-      <c r="G149" s="1"/>
+      <c r="F149" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H149" s="1"/>
       <c r="I149" s="3" t="s">
         <v>58</v>
@@ -41075,8 +42629,12 @@
         <v>364</v>
       </c>
       <c r="E150" s="1"/>
-      <c r="F150" s="1"/>
-      <c r="G150" s="1"/>
+      <c r="F150" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>1011</v>
+      </c>
       <c r="H150" s="1"/>
       <c r="I150" s="3" t="s">
         <v>58</v>
@@ -41096,8 +42654,12 @@
         <v>365</v>
       </c>
       <c r="E151" s="1"/>
-      <c r="F151" s="1"/>
-      <c r="G151" s="1"/>
+      <c r="F151" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H151" s="1"/>
       <c r="I151" s="3" t="s">
         <v>58</v>
@@ -41117,8 +42679,12 @@
         <v>365</v>
       </c>
       <c r="E152" s="1"/>
-      <c r="F152" s="1"/>
-      <c r="G152" s="1"/>
+      <c r="F152" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H152" s="1"/>
       <c r="I152" s="3" t="s">
         <v>58</v>
@@ -41138,8 +42704,12 @@
         <v>365</v>
       </c>
       <c r="E153" s="1"/>
-      <c r="F153" s="1"/>
-      <c r="G153" s="1"/>
+      <c r="F153" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H153" s="1"/>
       <c r="I153" s="3" t="s">
         <v>58</v>
@@ -41159,8 +42729,12 @@
         <v>366</v>
       </c>
       <c r="E154" s="1"/>
-      <c r="F154" s="1"/>
-      <c r="G154" s="1"/>
+      <c r="F154" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>1013</v>
+      </c>
       <c r="H154" s="1"/>
       <c r="I154" s="3" t="s">
         <v>58</v>
@@ -41180,8 +42754,12 @@
         <v>367</v>
       </c>
       <c r="E155" s="1"/>
-      <c r="F155" s="1"/>
-      <c r="G155" s="1"/>
+      <c r="F155" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H155" s="1"/>
       <c r="I155" s="3" t="s">
         <v>58</v>
@@ -41201,8 +42779,12 @@
         <v>367</v>
       </c>
       <c r="E156" s="1"/>
-      <c r="F156" s="1"/>
-      <c r="G156" s="1"/>
+      <c r="F156" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H156" s="1"/>
       <c r="I156" s="3" t="s">
         <v>58</v>
@@ -41222,8 +42804,12 @@
         <v>367</v>
       </c>
       <c r="E157" s="1"/>
-      <c r="F157" s="1"/>
-      <c r="G157" s="1"/>
+      <c r="F157" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H157" s="1"/>
       <c r="I157" s="3" t="s">
         <v>58</v>
@@ -41243,8 +42829,12 @@
         <v>367</v>
       </c>
       <c r="E158" s="1"/>
-      <c r="F158" s="1"/>
-      <c r="G158" s="1"/>
+      <c r="F158" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H158" s="1"/>
       <c r="I158" s="3" t="s">
         <v>58</v>
@@ -41264,8 +42854,12 @@
         <v>368</v>
       </c>
       <c r="E159" s="1"/>
-      <c r="F159" s="1"/>
-      <c r="G159" s="1"/>
+      <c r="F159" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H159" s="1"/>
       <c r="I159" s="3" t="s">
         <v>58</v>
@@ -41285,8 +42879,12 @@
         <v>368</v>
       </c>
       <c r="E160" s="1"/>
-      <c r="F160" s="1"/>
-      <c r="G160" s="1"/>
+      <c r="F160" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H160" s="1"/>
       <c r="I160" s="3" t="s">
         <v>58</v>
@@ -41306,8 +42904,12 @@
         <v>368</v>
       </c>
       <c r="E161" s="1"/>
-      <c r="F161" s="1"/>
-      <c r="G161" s="1"/>
+      <c r="F161" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H161" s="1"/>
       <c r="I161" s="3" t="s">
         <v>58</v>
@@ -41327,8 +42929,12 @@
         <v>368</v>
       </c>
       <c r="E162" s="1"/>
-      <c r="F162" s="1"/>
-      <c r="G162" s="1"/>
+      <c r="F162" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H162" s="1"/>
       <c r="I162" s="3" t="s">
         <v>58</v>
@@ -41348,8 +42954,12 @@
         <v>368</v>
       </c>
       <c r="E163" s="1"/>
-      <c r="F163" s="1"/>
-      <c r="G163" s="1"/>
+      <c r="F163" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H163" s="1"/>
       <c r="I163" s="3" t="s">
         <v>58</v>
@@ -41369,8 +42979,12 @@
         <v>368</v>
       </c>
       <c r="E164" s="1"/>
-      <c r="F164" s="1"/>
-      <c r="G164" s="1"/>
+      <c r="F164" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H164" s="1"/>
       <c r="I164" s="3" t="s">
         <v>58</v>
@@ -41390,8 +43004,12 @@
         <v>361</v>
       </c>
       <c r="E165" s="1"/>
-      <c r="F165" s="1"/>
-      <c r="G165" s="1"/>
+      <c r="F165" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H165" s="1"/>
       <c r="I165" s="3" t="s">
         <v>58</v>
@@ -41411,8 +43029,12 @@
         <v>362</v>
       </c>
       <c r="E166" s="1"/>
-      <c r="F166" s="1"/>
-      <c r="G166" s="1"/>
+      <c r="F166" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H166" s="1"/>
       <c r="I166" s="3" t="s">
         <v>58</v>
@@ -41432,8 +43054,12 @@
         <v>362</v>
       </c>
       <c r="E167" s="1"/>
-      <c r="F167" s="1"/>
-      <c r="G167" s="1"/>
+      <c r="F167" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H167" s="1"/>
       <c r="I167" s="3" t="s">
         <v>58</v>
@@ -41453,8 +43079,12 @@
         <v>362</v>
       </c>
       <c r="E168" s="1"/>
-      <c r="F168" s="1"/>
-      <c r="G168" s="1"/>
+      <c r="F168" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H168" s="1"/>
       <c r="I168" s="3" t="s">
         <v>58</v>
@@ -41474,8 +43104,12 @@
         <v>363</v>
       </c>
       <c r="E169" s="1"/>
-      <c r="F169" s="1"/>
-      <c r="G169" s="1"/>
+      <c r="F169" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H169" s="1"/>
       <c r="I169" s="3" t="s">
         <v>58</v>
@@ -41495,8 +43129,12 @@
         <v>363</v>
       </c>
       <c r="E170" s="1"/>
-      <c r="F170" s="1"/>
-      <c r="G170" s="1"/>
+      <c r="F170" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H170" s="1"/>
       <c r="I170" s="3" t="s">
         <v>58</v>
@@ -41516,8 +43154,12 @@
         <v>363</v>
       </c>
       <c r="E171" s="1"/>
-      <c r="F171" s="1"/>
-      <c r="G171" s="1"/>
+      <c r="F171" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H171" s="1"/>
       <c r="I171" s="3" t="s">
         <v>58</v>
@@ -41537,8 +43179,12 @@
         <v>363</v>
       </c>
       <c r="E172" s="1"/>
-      <c r="F172" s="1"/>
-      <c r="G172" s="1"/>
+      <c r="F172" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H172" s="1"/>
       <c r="I172" s="3" t="s">
         <v>58</v>
@@ -41558,8 +43204,12 @@
         <v>363</v>
       </c>
       <c r="E173" s="1"/>
-      <c r="F173" s="1"/>
-      <c r="G173" s="1"/>
+      <c r="F173" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H173" s="1"/>
       <c r="I173" s="3" t="s">
         <v>58</v>
@@ -41579,8 +43229,12 @@
         <v>364</v>
       </c>
       <c r="E174" s="1"/>
-      <c r="F174" s="1"/>
-      <c r="G174" s="1"/>
+      <c r="F174" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>1011</v>
+      </c>
       <c r="H174" s="1"/>
       <c r="I174" s="3" t="s">
         <v>58</v>
@@ -41600,8 +43254,12 @@
         <v>365</v>
       </c>
       <c r="E175" s="1"/>
-      <c r="F175" s="1"/>
-      <c r="G175" s="1"/>
+      <c r="F175" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H175" s="1"/>
       <c r="I175" s="3" t="s">
         <v>58</v>
@@ -41621,8 +43279,12 @@
         <v>365</v>
       </c>
       <c r="E176" s="1"/>
-      <c r="F176" s="1"/>
-      <c r="G176" s="1"/>
+      <c r="F176" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H176" s="1"/>
       <c r="I176" s="3" t="s">
         <v>58</v>
@@ -41642,8 +43304,12 @@
         <v>365</v>
       </c>
       <c r="E177" s="1"/>
-      <c r="F177" s="1"/>
-      <c r="G177" s="1"/>
+      <c r="F177" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H177" s="1"/>
       <c r="I177" s="3" t="s">
         <v>58</v>
@@ -41663,8 +43329,12 @@
         <v>366</v>
       </c>
       <c r="E178" s="1"/>
-      <c r="F178" s="1"/>
-      <c r="G178" s="1"/>
+      <c r="F178" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>1013</v>
+      </c>
       <c r="H178" s="1"/>
       <c r="I178" s="3" t="s">
         <v>58</v>
@@ -41684,8 +43354,12 @@
         <v>367</v>
       </c>
       <c r="E179" s="1"/>
-      <c r="F179" s="1"/>
-      <c r="G179" s="1"/>
+      <c r="F179" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H179" s="1"/>
       <c r="I179" s="3" t="s">
         <v>58</v>
@@ -41705,8 +43379,12 @@
         <v>367</v>
       </c>
       <c r="E180" s="1"/>
-      <c r="F180" s="1"/>
-      <c r="G180" s="1"/>
+      <c r="F180" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H180" s="1"/>
       <c r="I180" s="3" t="s">
         <v>58</v>
@@ -41726,8 +43404,12 @@
         <v>367</v>
       </c>
       <c r="E181" s="1"/>
-      <c r="F181" s="1"/>
-      <c r="G181" s="1"/>
+      <c r="F181" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H181" s="1"/>
       <c r="I181" s="3" t="s">
         <v>58</v>
@@ -41747,8 +43429,12 @@
         <v>367</v>
       </c>
       <c r="E182" s="1"/>
-      <c r="F182" s="1"/>
-      <c r="G182" s="1"/>
+      <c r="F182" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H182" s="1"/>
       <c r="I182" s="3" t="s">
         <v>58</v>
@@ -41768,8 +43454,12 @@
         <v>368</v>
       </c>
       <c r="E183" s="1"/>
-      <c r="F183" s="1"/>
-      <c r="G183" s="1"/>
+      <c r="F183" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H183" s="1"/>
       <c r="I183" s="3" t="s">
         <v>58</v>
@@ -41789,8 +43479,12 @@
         <v>368</v>
       </c>
       <c r="E184" s="1"/>
-      <c r="F184" s="1"/>
-      <c r="G184" s="1"/>
+      <c r="F184" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H184" s="1"/>
       <c r="I184" s="3" t="s">
         <v>58</v>
@@ -41810,8 +43504,12 @@
         <v>368</v>
       </c>
       <c r="E185" s="1"/>
-      <c r="F185" s="1"/>
-      <c r="G185" s="1"/>
+      <c r="F185" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H185" s="1"/>
       <c r="I185" s="3" t="s">
         <v>58</v>
@@ -41831,8 +43529,12 @@
         <v>368</v>
       </c>
       <c r="E186" s="1"/>
-      <c r="F186" s="1"/>
-      <c r="G186" s="1"/>
+      <c r="F186" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H186" s="1"/>
       <c r="I186" s="3" t="s">
         <v>58</v>
@@ -41852,8 +43554,12 @@
         <v>368</v>
       </c>
       <c r="E187" s="1"/>
-      <c r="F187" s="1"/>
-      <c r="G187" s="1"/>
+      <c r="F187" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H187" s="1"/>
       <c r="I187" s="3" t="s">
         <v>58</v>
@@ -41873,8 +43579,12 @@
         <v>368</v>
       </c>
       <c r="E188" s="1"/>
-      <c r="F188" s="1"/>
-      <c r="G188" s="1"/>
+      <c r="F188" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H188" s="1"/>
       <c r="I188" s="3" t="s">
         <v>58</v>
@@ -41894,8 +43604,12 @@
         <v>361</v>
       </c>
       <c r="E189" s="1"/>
-      <c r="F189" s="1"/>
-      <c r="G189" s="1"/>
+      <c r="F189" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H189" s="1"/>
       <c r="I189" s="3" t="s">
         <v>58</v>
@@ -41915,8 +43629,12 @@
         <v>362</v>
       </c>
       <c r="E190" s="1"/>
-      <c r="F190" s="1"/>
-      <c r="G190" s="1"/>
+      <c r="F190" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H190" s="1"/>
       <c r="I190" s="3" t="s">
         <v>58</v>
@@ -41936,8 +43654,12 @@
         <v>362</v>
       </c>
       <c r="E191" s="1"/>
-      <c r="F191" s="1"/>
-      <c r="G191" s="1"/>
+      <c r="F191" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H191" s="1"/>
       <c r="I191" s="3" t="s">
         <v>58</v>
@@ -41957,8 +43679,12 @@
         <v>362</v>
       </c>
       <c r="E192" s="1"/>
-      <c r="F192" s="1"/>
-      <c r="G192" s="1"/>
+      <c r="F192" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H192" s="1"/>
       <c r="I192" s="3" t="s">
         <v>58</v>
@@ -41978,8 +43704,12 @@
         <v>363</v>
       </c>
       <c r="E193" s="1"/>
-      <c r="F193" s="1"/>
-      <c r="G193" s="1"/>
+      <c r="F193" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H193" s="1"/>
       <c r="I193" s="3" t="s">
         <v>58</v>
@@ -41999,8 +43729,12 @@
         <v>363</v>
       </c>
       <c r="E194" s="1"/>
-      <c r="F194" s="1"/>
-      <c r="G194" s="1"/>
+      <c r="F194" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H194" s="1"/>
       <c r="I194" s="3" t="s">
         <v>58</v>
@@ -42020,8 +43754,12 @@
         <v>363</v>
       </c>
       <c r="E195" s="1"/>
-      <c r="F195" s="1"/>
-      <c r="G195" s="1"/>
+      <c r="F195" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H195" s="1"/>
       <c r="I195" s="3" t="s">
         <v>58</v>
@@ -42041,8 +43779,12 @@
         <v>363</v>
       </c>
       <c r="E196" s="1"/>
-      <c r="F196" s="1"/>
-      <c r="G196" s="1"/>
+      <c r="F196" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H196" s="1"/>
       <c r="I196" s="3" t="s">
         <v>58</v>
@@ -42062,8 +43804,12 @@
         <v>363</v>
       </c>
       <c r="E197" s="1"/>
-      <c r="F197" s="1"/>
-      <c r="G197" s="1"/>
+      <c r="F197" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H197" s="1"/>
       <c r="I197" s="3" t="s">
         <v>58</v>
@@ -42083,8 +43829,12 @@
         <v>364</v>
       </c>
       <c r="E198" s="1"/>
-      <c r="F198" s="1"/>
-      <c r="G198" s="1"/>
+      <c r="F198" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>1011</v>
+      </c>
       <c r="H198" s="1"/>
       <c r="I198" s="3" t="s">
         <v>58</v>
@@ -42104,8 +43854,12 @@
         <v>365</v>
       </c>
       <c r="E199" s="1"/>
-      <c r="F199" s="1"/>
-      <c r="G199" s="1"/>
+      <c r="F199" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H199" s="1"/>
       <c r="I199" s="3" t="s">
         <v>58</v>
@@ -42125,8 +43879,12 @@
         <v>365</v>
       </c>
       <c r="E200" s="1"/>
-      <c r="F200" s="1"/>
-      <c r="G200" s="1"/>
+      <c r="F200" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H200" s="1"/>
       <c r="I200" s="3" t="s">
         <v>58</v>
@@ -42146,8 +43904,12 @@
         <v>365</v>
       </c>
       <c r="E201" s="1"/>
-      <c r="F201" s="1"/>
-      <c r="G201" s="1"/>
+      <c r="F201" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H201" s="1"/>
       <c r="I201" s="3" t="s">
         <v>58</v>
@@ -42167,8 +43929,12 @@
         <v>366</v>
       </c>
       <c r="E202" s="1"/>
-      <c r="F202" s="1"/>
-      <c r="G202" s="1"/>
+      <c r="F202" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>1013</v>
+      </c>
       <c r="H202" s="1"/>
       <c r="I202" s="3" t="s">
         <v>58</v>
@@ -42188,8 +43954,12 @@
         <v>367</v>
       </c>
       <c r="E203" s="1"/>
-      <c r="F203" s="1"/>
-      <c r="G203" s="1"/>
+      <c r="F203" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H203" s="1"/>
       <c r="I203" s="3" t="s">
         <v>58</v>
@@ -42209,8 +43979,12 @@
         <v>367</v>
       </c>
       <c r="E204" s="1"/>
-      <c r="F204" s="1"/>
-      <c r="G204" s="1"/>
+      <c r="F204" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H204" s="1"/>
       <c r="I204" s="3" t="s">
         <v>58</v>
@@ -42230,8 +44004,12 @@
         <v>367</v>
       </c>
       <c r="E205" s="1"/>
-      <c r="F205" s="1"/>
-      <c r="G205" s="1"/>
+      <c r="F205" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H205" s="1"/>
       <c r="I205" s="3" t="s">
         <v>58</v>
@@ -42251,8 +44029,12 @@
         <v>367</v>
       </c>
       <c r="E206" s="1"/>
-      <c r="F206" s="1"/>
-      <c r="G206" s="1"/>
+      <c r="F206" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H206" s="1"/>
       <c r="I206" s="3" t="s">
         <v>58</v>
@@ -42272,8 +44054,12 @@
         <v>368</v>
       </c>
       <c r="E207" s="1"/>
-      <c r="F207" s="1"/>
-      <c r="G207" s="1"/>
+      <c r="F207" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H207" s="1"/>
       <c r="I207" s="3" t="s">
         <v>58</v>
@@ -42293,8 +44079,12 @@
         <v>368</v>
       </c>
       <c r="E208" s="1"/>
-      <c r="F208" s="1"/>
-      <c r="G208" s="1"/>
+      <c r="F208" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H208" s="1"/>
       <c r="I208" s="3" t="s">
         <v>58</v>
@@ -42314,8 +44104,12 @@
         <v>368</v>
       </c>
       <c r="E209" s="1"/>
-      <c r="F209" s="1"/>
-      <c r="G209" s="1"/>
+      <c r="F209" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H209" s="1"/>
       <c r="I209" s="3" t="s">
         <v>58</v>
@@ -42335,8 +44129,12 @@
         <v>368</v>
       </c>
       <c r="E210" s="1"/>
-      <c r="F210" s="1"/>
-      <c r="G210" s="1"/>
+      <c r="F210" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H210" s="1"/>
       <c r="I210" s="3" t="s">
         <v>58</v>
@@ -42356,8 +44154,12 @@
         <v>368</v>
       </c>
       <c r="E211" s="1"/>
-      <c r="F211" s="1"/>
-      <c r="G211" s="1"/>
+      <c r="F211" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H211" s="1"/>
       <c r="I211" s="3" t="s">
         <v>58</v>
@@ -42377,8 +44179,12 @@
         <v>368</v>
       </c>
       <c r="E212" s="1"/>
-      <c r="F212" s="1"/>
-      <c r="G212" s="1"/>
+      <c r="F212" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H212" s="1"/>
       <c r="I212" s="3" t="s">
         <v>58</v>
@@ -42398,8 +44204,12 @@
         <v>361</v>
       </c>
       <c r="E213" s="1"/>
-      <c r="F213" s="1"/>
-      <c r="G213" s="1"/>
+      <c r="F213" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H213" s="1"/>
       <c r="I213" s="3" t="s">
         <v>58</v>
@@ -42419,8 +44229,12 @@
         <v>362</v>
       </c>
       <c r="E214" s="1"/>
-      <c r="F214" s="1"/>
-      <c r="G214" s="1"/>
+      <c r="F214" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H214" s="1"/>
       <c r="I214" s="3" t="s">
         <v>58</v>
@@ -42440,8 +44254,12 @@
         <v>362</v>
       </c>
       <c r="E215" s="1"/>
-      <c r="F215" s="1"/>
-      <c r="G215" s="1"/>
+      <c r="F215" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H215" s="1"/>
       <c r="I215" s="3" t="s">
         <v>58</v>
@@ -42461,8 +44279,12 @@
         <v>362</v>
       </c>
       <c r="E216" s="1"/>
-      <c r="F216" s="1"/>
-      <c r="G216" s="1"/>
+      <c r="F216" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H216" s="1"/>
       <c r="I216" s="3" t="s">
         <v>58</v>
@@ -42482,8 +44304,12 @@
         <v>363</v>
       </c>
       <c r="E217" s="1"/>
-      <c r="F217" s="1"/>
-      <c r="G217" s="1"/>
+      <c r="F217" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H217" s="1"/>
       <c r="I217" s="3" t="s">
         <v>58</v>
@@ -42503,8 +44329,12 @@
         <v>363</v>
       </c>
       <c r="E218" s="1"/>
-      <c r="F218" s="1"/>
-      <c r="G218" s="1"/>
+      <c r="F218" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H218" s="1"/>
       <c r="I218" s="3" t="s">
         <v>58</v>
@@ -42524,8 +44354,12 @@
         <v>363</v>
       </c>
       <c r="E219" s="1"/>
-      <c r="F219" s="1"/>
-      <c r="G219" s="1"/>
+      <c r="F219" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H219" s="1"/>
       <c r="I219" s="3" t="s">
         <v>58</v>
@@ -42545,8 +44379,12 @@
         <v>363</v>
       </c>
       <c r="E220" s="1"/>
-      <c r="F220" s="1"/>
-      <c r="G220" s="1"/>
+      <c r="F220" s="3" t="s">
+        <v>917</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H220" s="1"/>
       <c r="I220" s="3" t="s">
         <v>58</v>
@@ -42566,8 +44404,12 @@
         <v>363</v>
       </c>
       <c r="E221" s="1"/>
-      <c r="F221" s="1"/>
-      <c r="G221" s="1"/>
+      <c r="F221" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H221" s="1"/>
       <c r="I221" s="3" t="s">
         <v>58</v>
@@ -42587,8 +44429,12 @@
         <v>364</v>
       </c>
       <c r="E222" s="1"/>
-      <c r="F222" s="1"/>
-      <c r="G222" s="1"/>
+      <c r="F222" s="3" t="s">
+        <v>919</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>1011</v>
+      </c>
       <c r="H222" s="1"/>
       <c r="I222" s="3" t="s">
         <v>58</v>
@@ -42608,8 +44454,12 @@
         <v>365</v>
       </c>
       <c r="E223" s="1"/>
-      <c r="F223" s="1"/>
-      <c r="G223" s="1"/>
+      <c r="F223" s="3" t="s">
+        <v>920</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H223" s="1"/>
       <c r="I223" s="3" t="s">
         <v>58</v>
@@ -42629,8 +44479,12 @@
         <v>365</v>
       </c>
       <c r="E224" s="1"/>
-      <c r="F224" s="1"/>
-      <c r="G224" s="1"/>
+      <c r="F224" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H224" s="1"/>
       <c r="I224" s="3" t="s">
         <v>58</v>
@@ -42650,8 +44504,12 @@
         <v>365</v>
       </c>
       <c r="E225" s="1"/>
-      <c r="F225" s="1"/>
-      <c r="G225" s="1"/>
+      <c r="F225" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H225" s="1"/>
       <c r="I225" s="3" t="s">
         <v>58</v>
@@ -42671,8 +44529,12 @@
         <v>366</v>
       </c>
       <c r="E226" s="1"/>
-      <c r="F226" s="1"/>
-      <c r="G226" s="1"/>
+      <c r="F226" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>1013</v>
+      </c>
       <c r="H226" s="1"/>
       <c r="I226" s="3" t="s">
         <v>58</v>
@@ -42692,8 +44554,12 @@
         <v>367</v>
       </c>
       <c r="E227" s="1"/>
-      <c r="F227" s="1"/>
-      <c r="G227" s="1"/>
+      <c r="F227" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H227" s="1"/>
       <c r="I227" s="3" t="s">
         <v>58</v>
@@ -42713,8 +44579,12 @@
         <v>367</v>
       </c>
       <c r="E228" s="1"/>
-      <c r="F228" s="1"/>
-      <c r="G228" s="1"/>
+      <c r="F228" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H228" s="1"/>
       <c r="I228" s="3" t="s">
         <v>58</v>
@@ -42734,8 +44604,12 @@
         <v>367</v>
       </c>
       <c r="E229" s="1"/>
-      <c r="F229" s="1"/>
-      <c r="G229" s="1"/>
+      <c r="F229" s="3" t="s">
+        <v>926</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H229" s="1"/>
       <c r="I229" s="3" t="s">
         <v>58</v>
@@ -42755,8 +44629,12 @@
         <v>367</v>
       </c>
       <c r="E230" s="1"/>
-      <c r="F230" s="1"/>
-      <c r="G230" s="1"/>
+      <c r="F230" s="3" t="s">
+        <v>927</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H230" s="1"/>
       <c r="I230" s="3" t="s">
         <v>58</v>
@@ -42776,8 +44654,12 @@
         <v>368</v>
       </c>
       <c r="E231" s="1"/>
-      <c r="F231" s="1"/>
-      <c r="G231" s="1"/>
+      <c r="F231" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H231" s="1"/>
       <c r="I231" s="3" t="s">
         <v>58</v>
@@ -42797,8 +44679,12 @@
         <v>368</v>
       </c>
       <c r="E232" s="1"/>
-      <c r="F232" s="1"/>
-      <c r="G232" s="1"/>
+      <c r="F232" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H232" s="1"/>
       <c r="I232" s="3" t="s">
         <v>58</v>
@@ -42818,8 +44704,12 @@
         <v>368</v>
       </c>
       <c r="E233" s="1"/>
-      <c r="F233" s="1"/>
-      <c r="G233" s="1"/>
+      <c r="F233" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H233" s="1"/>
       <c r="I233" s="3" t="s">
         <v>58</v>
@@ -42839,8 +44729,12 @@
         <v>368</v>
       </c>
       <c r="E234" s="1"/>
-      <c r="F234" s="1"/>
-      <c r="G234" s="1"/>
+      <c r="F234" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H234" s="1"/>
       <c r="I234" s="3" t="s">
         <v>58</v>
@@ -42860,8 +44754,12 @@
         <v>368</v>
       </c>
       <c r="E235" s="1"/>
-      <c r="F235" s="1"/>
-      <c r="G235" s="1"/>
+      <c r="F235" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H235" s="1"/>
       <c r="I235" s="3" t="s">
         <v>58</v>
@@ -42881,8 +44779,12 @@
         <v>368</v>
       </c>
       <c r="E236" s="1"/>
-      <c r="F236" s="1"/>
-      <c r="G236" s="1"/>
+      <c r="F236" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H236" s="1"/>
       <c r="I236" s="3" t="s">
         <v>58</v>
@@ -42902,8 +44804,12 @@
         <v>361</v>
       </c>
       <c r="E237" s="1"/>
-      <c r="F237" s="1"/>
-      <c r="G237" s="1"/>
+      <c r="F237" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H237" s="1"/>
       <c r="I237" s="3" t="s">
         <v>58</v>
@@ -42923,8 +44829,12 @@
         <v>362</v>
       </c>
       <c r="E238" s="1"/>
-      <c r="F238" s="1"/>
-      <c r="G238" s="1"/>
+      <c r="F238" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H238" s="1"/>
       <c r="I238" s="3" t="s">
         <v>58</v>
@@ -42944,8 +44854,12 @@
         <v>362</v>
       </c>
       <c r="E239" s="1"/>
-      <c r="F239" s="1"/>
-      <c r="G239" s="1"/>
+      <c r="F239" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H239" s="1"/>
       <c r="I239" s="3" t="s">
         <v>58</v>
@@ -42965,8 +44879,12 @@
         <v>362</v>
       </c>
       <c r="E240" s="1"/>
-      <c r="F240" s="1"/>
-      <c r="G240" s="1"/>
+      <c r="F240" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H240" s="1"/>
       <c r="I240" s="3" t="s">
         <v>58</v>
@@ -42986,8 +44904,12 @@
         <v>363</v>
       </c>
       <c r="E241" s="1"/>
-      <c r="F241" s="1"/>
-      <c r="G241" s="1"/>
+      <c r="F241" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H241" s="1"/>
       <c r="I241" s="3" t="s">
         <v>58</v>
@@ -43007,8 +44929,12 @@
         <v>363</v>
       </c>
       <c r="E242" s="1"/>
-      <c r="F242" s="1"/>
-      <c r="G242" s="1"/>
+      <c r="F242" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H242" s="1"/>
       <c r="I242" s="3" t="s">
         <v>58</v>
@@ -43028,8 +44954,12 @@
         <v>363</v>
       </c>
       <c r="E243" s="1"/>
-      <c r="F243" s="1"/>
-      <c r="G243" s="1"/>
+      <c r="F243" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H243" s="1"/>
       <c r="I243" s="3" t="s">
         <v>58</v>
@@ -43049,8 +44979,12 @@
         <v>363</v>
       </c>
       <c r="E244" s="10"/>
-      <c r="F244" s="3"/>
-      <c r="G244" s="3"/>
+      <c r="F244" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>1010</v>
+      </c>
       <c r="H244" s="4"/>
       <c r="I244" s="3" t="s">
         <v>58</v>
@@ -43070,8 +45004,12 @@
         <v>363</v>
       </c>
       <c r="E245" s="10"/>
-      <c r="F245" s="3"/>
-      <c r="G245" s="4"/>
+      <c r="F245" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="G245" s="4" t="s">
+        <v>1010</v>
+      </c>
       <c r="H245" s="4"/>
       <c r="I245" s="3" t="s">
         <v>58</v>
@@ -43091,8 +45029,12 @@
         <v>364</v>
       </c>
       <c r="E246" s="10"/>
-      <c r="F246" s="3"/>
-      <c r="G246" s="4"/>
+      <c r="F246" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="G246" s="4" t="s">
+        <v>1011</v>
+      </c>
       <c r="H246" s="4"/>
       <c r="I246" s="3" t="s">
         <v>58</v>
@@ -43112,8 +45054,12 @@
         <v>365</v>
       </c>
       <c r="E247" s="10"/>
-      <c r="F247" s="3"/>
-      <c r="G247" s="3"/>
+      <c r="F247" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H247" s="4"/>
       <c r="I247" s="3" t="s">
         <v>58</v>
@@ -43133,8 +45079,12 @@
         <v>365</v>
       </c>
       <c r="E248" s="10"/>
-      <c r="F248" s="3"/>
-      <c r="G248" s="3"/>
+      <c r="F248" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H248" s="4"/>
       <c r="I248" s="3" t="s">
         <v>58</v>
@@ -43154,8 +45104,12 @@
         <v>365</v>
       </c>
       <c r="E249" s="10"/>
-      <c r="F249" s="3"/>
-      <c r="G249" s="3"/>
+      <c r="F249" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>1012</v>
+      </c>
       <c r="H249" s="4"/>
       <c r="I249" s="3" t="s">
         <v>58</v>
@@ -43175,8 +45129,12 @@
         <v>366</v>
       </c>
       <c r="E250" s="4"/>
-      <c r="F250" s="3"/>
-      <c r="G250" s="3"/>
+      <c r="F250" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>1013</v>
+      </c>
       <c r="H250" s="4"/>
       <c r="I250" s="3" t="s">
         <v>58</v>
@@ -43196,8 +45154,12 @@
         <v>367</v>
       </c>
       <c r="E251" s="4"/>
-      <c r="F251" s="3"/>
-      <c r="G251" s="3"/>
+      <c r="F251" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H251" s="4"/>
       <c r="I251" s="3" t="s">
         <v>58</v>
@@ -43217,8 +45179,12 @@
         <v>367</v>
       </c>
       <c r="E252" s="4"/>
-      <c r="F252" s="3"/>
-      <c r="G252" s="3"/>
+      <c r="F252" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H252" s="4"/>
       <c r="I252" s="3" t="s">
         <v>58</v>
@@ -43238,8 +45204,12 @@
         <v>367</v>
       </c>
       <c r="E253" s="4"/>
-      <c r="F253" s="3"/>
-      <c r="G253" s="3"/>
+      <c r="F253" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="H253" s="4"/>
       <c r="I253" s="3" t="s">
         <v>58</v>
@@ -43259,8 +45229,12 @@
         <v>367</v>
       </c>
       <c r="E254" s="3"/>
-      <c r="F254" s="3"/>
-      <c r="G254" s="4"/>
+      <c r="F254" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="G254" s="4" t="s">
+        <v>1014</v>
+      </c>
       <c r="H254" s="4"/>
       <c r="I254" s="3" t="s">
         <v>58</v>
@@ -43280,8 +45254,12 @@
         <v>368</v>
       </c>
       <c r="E255" s="4"/>
-      <c r="F255" s="3"/>
-      <c r="G255" s="3"/>
+      <c r="F255" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="G255" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H255" s="4"/>
       <c r="I255" s="3" t="s">
         <v>58</v>
@@ -43301,8 +45279,12 @@
         <v>368</v>
       </c>
       <c r="E256" s="4"/>
-      <c r="F256" s="3"/>
-      <c r="G256" s="3"/>
+      <c r="F256" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H256" s="4"/>
       <c r="I256" s="3" t="s">
         <v>58</v>
@@ -43322,8 +45304,12 @@
         <v>368</v>
       </c>
       <c r="E257" s="4"/>
-      <c r="F257" s="3"/>
-      <c r="G257" s="3"/>
+      <c r="F257" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="G257" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H257" s="4"/>
       <c r="I257" s="3" t="s">
         <v>58</v>
@@ -43343,8 +45329,12 @@
         <v>368</v>
       </c>
       <c r="E258" s="4"/>
-      <c r="F258" s="3"/>
-      <c r="G258" s="3"/>
+      <c r="F258" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H258" s="3"/>
       <c r="I258" s="3" t="s">
         <v>58</v>
@@ -43364,8 +45354,12 @@
         <v>368</v>
       </c>
       <c r="E259" s="4"/>
-      <c r="F259" s="3"/>
-      <c r="G259" s="3"/>
+      <c r="F259" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="G259" s="3" t="s">
+        <v>1015</v>
+      </c>
       <c r="H259" s="3"/>
       <c r="I259" s="3" t="s">
         <v>58</v>
@@ -43385,8 +45379,12 @@
         <v>368</v>
       </c>
       <c r="E260" s="3"/>
-      <c r="F260" s="3"/>
-      <c r="G260" s="4"/>
+      <c r="F260" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="G260" s="4" t="s">
+        <v>1015</v>
+      </c>
       <c r="H260" s="4"/>
       <c r="I260" s="3" t="s">
         <v>58</v>
@@ -43406,8 +45404,12 @@
         <v>362</v>
       </c>
       <c r="E261" s="4"/>
-      <c r="F261" s="3"/>
-      <c r="G261" s="3"/>
+      <c r="F261" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="G261" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H261" s="4"/>
       <c r="I261" s="3" t="s">
         <v>58</v>
@@ -43427,8 +45429,12 @@
         <v>364</v>
       </c>
       <c r="E262" s="4"/>
-      <c r="F262" s="3"/>
-      <c r="G262" s="3"/>
+      <c r="F262" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>1011</v>
+      </c>
       <c r="H262" s="4"/>
       <c r="I262" s="3" t="s">
         <v>58</v>
@@ -43448,8 +45454,12 @@
         <v>361</v>
       </c>
       <c r="E263" s="4"/>
-      <c r="F263" s="3"/>
-      <c r="G263" s="3"/>
+      <c r="F263" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="G263" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H263" s="4"/>
       <c r="I263" s="3" t="s">
         <v>58</v>
@@ -43469,8 +45479,12 @@
         <v>361</v>
       </c>
       <c r="E264" s="4"/>
-      <c r="F264" s="3"/>
-      <c r="G264" s="3"/>
+      <c r="F264" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="G264" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H264" s="4"/>
       <c r="I264" s="3" t="s">
         <v>58</v>
@@ -43490,8 +45504,12 @@
         <v>361</v>
       </c>
       <c r="E265" s="3"/>
-      <c r="F265" s="3"/>
-      <c r="G265" s="4"/>
+      <c r="F265" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="G265" s="4" t="s">
+        <v>1008</v>
+      </c>
       <c r="H265" s="4"/>
       <c r="I265" s="3" t="s">
         <v>58</v>
@@ -43511,8 +45529,12 @@
         <v>362</v>
       </c>
       <c r="E266" s="3"/>
-      <c r="F266" s="3"/>
-      <c r="G266" s="4"/>
+      <c r="F266" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="G266" s="4" t="s">
+        <v>1009</v>
+      </c>
       <c r="H266" s="4"/>
       <c r="I266" s="3" t="s">
         <v>58</v>
@@ -43532,8 +45554,12 @@
         <v>364</v>
       </c>
       <c r="E267" s="3"/>
-      <c r="F267" s="3"/>
-      <c r="G267" s="4"/>
+      <c r="F267" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="G267" s="4" t="s">
+        <v>1011</v>
+      </c>
       <c r="H267" s="4"/>
       <c r="I267" s="3" t="s">
         <v>58</v>
@@ -43553,8 +45579,12 @@
         <v>361</v>
       </c>
       <c r="E268" s="4"/>
-      <c r="F268" s="3"/>
-      <c r="G268" s="3"/>
+      <c r="F268" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="G268" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H268" s="4"/>
       <c r="I268" s="3" t="s">
         <v>58</v>
@@ -43574,8 +45604,12 @@
         <v>361</v>
       </c>
       <c r="E269" s="3"/>
-      <c r="F269" s="3"/>
-      <c r="G269" s="4"/>
+      <c r="F269" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="G269" s="4" t="s">
+        <v>1008</v>
+      </c>
       <c r="H269" s="4"/>
       <c r="I269" s="3" t="s">
         <v>58</v>
@@ -43595,8 +45629,12 @@
         <v>361</v>
       </c>
       <c r="E270" s="3"/>
-      <c r="F270" s="3"/>
-      <c r="G270" s="4"/>
+      <c r="F270" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="G270" s="4" t="s">
+        <v>1008</v>
+      </c>
       <c r="H270" s="4"/>
       <c r="I270" s="3" t="s">
         <v>58</v>
@@ -43616,8 +45654,12 @@
         <v>362</v>
       </c>
       <c r="E271" s="4"/>
-      <c r="F271" s="3"/>
-      <c r="G271" s="3"/>
+      <c r="F271" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="G271" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H271" s="4"/>
       <c r="I271" s="3" t="s">
         <v>58</v>
@@ -43637,8 +45679,12 @@
         <v>364</v>
       </c>
       <c r="E272" s="4"/>
-      <c r="F272" s="3"/>
-      <c r="G272" s="3"/>
+      <c r="F272" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="G272" s="3" t="s">
+        <v>1011</v>
+      </c>
       <c r="H272" s="4"/>
       <c r="I272" s="3" t="s">
         <v>58</v>
@@ -43658,8 +45704,12 @@
         <v>361</v>
       </c>
       <c r="E273" s="4"/>
-      <c r="F273" s="3"/>
-      <c r="G273" s="3"/>
+      <c r="F273" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="G273" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H273" s="4"/>
       <c r="I273" s="3" t="s">
         <v>58</v>
@@ -43679,8 +45729,12 @@
         <v>361</v>
       </c>
       <c r="E274" s="4"/>
-      <c r="F274" s="3"/>
-      <c r="G274" s="3"/>
+      <c r="F274" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="G274" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H274" s="4"/>
       <c r="I274" s="3" t="s">
         <v>58</v>
@@ -43700,8 +45754,12 @@
         <v>361</v>
       </c>
       <c r="E275" s="4"/>
-      <c r="F275" s="3"/>
-      <c r="G275" s="3"/>
+      <c r="F275" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H275" s="4"/>
       <c r="I275" s="3" t="s">
         <v>58</v>
@@ -43721,8 +45779,12 @@
         <v>362</v>
       </c>
       <c r="E276" s="4"/>
-      <c r="F276" s="3"/>
-      <c r="G276" s="3"/>
+      <c r="F276" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="G276" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H276" s="4"/>
       <c r="I276" s="3" t="s">
         <v>58</v>
@@ -43742,8 +45804,12 @@
         <v>364</v>
       </c>
       <c r="E277" s="4"/>
-      <c r="F277" s="3"/>
-      <c r="G277" s="3"/>
+      <c r="F277" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="G277" s="3" t="s">
+        <v>1011</v>
+      </c>
       <c r="H277" s="4"/>
       <c r="I277" s="3" t="s">
         <v>58</v>
@@ -43763,8 +45829,12 @@
         <v>361</v>
       </c>
       <c r="E278" s="3"/>
-      <c r="F278" s="3"/>
-      <c r="G278" s="4"/>
+      <c r="F278" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="G278" s="4" t="s">
+        <v>1008</v>
+      </c>
       <c r="H278" s="4"/>
       <c r="I278" s="3" t="s">
         <v>58</v>
@@ -43784,8 +45854,12 @@
         <v>361</v>
       </c>
       <c r="E279" s="4"/>
-      <c r="F279" s="3"/>
-      <c r="G279" s="3"/>
+      <c r="F279" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="G279" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H279" s="4"/>
       <c r="I279" s="3" t="s">
         <v>58</v>
@@ -43805,8 +45879,12 @@
         <v>361</v>
       </c>
       <c r="E280" s="4"/>
-      <c r="F280" s="3"/>
-      <c r="G280" s="3"/>
+      <c r="F280" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="G280" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H280" s="4"/>
       <c r="I280" s="3" t="s">
         <v>58</v>
@@ -43826,8 +45904,12 @@
         <v>362</v>
       </c>
       <c r="E281" s="3"/>
-      <c r="F281" s="3"/>
-      <c r="G281" s="3"/>
+      <c r="F281" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="G281" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H281" s="3"/>
       <c r="I281" s="3" t="s">
         <v>58</v>
@@ -43847,8 +45929,12 @@
         <v>364</v>
       </c>
       <c r="E282" s="3"/>
-      <c r="F282" s="3"/>
-      <c r="G282" s="3"/>
+      <c r="F282" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="G282" s="3" t="s">
+        <v>1011</v>
+      </c>
       <c r="H282" s="3"/>
       <c r="I282" s="3" t="s">
         <v>58</v>
@@ -43868,8 +45954,12 @@
         <v>361</v>
       </c>
       <c r="E283" s="3"/>
-      <c r="F283" s="3"/>
-      <c r="G283" s="3"/>
+      <c r="F283" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="G283" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H283" s="3"/>
       <c r="I283" s="3" t="s">
         <v>58</v>
@@ -43889,8 +45979,12 @@
         <v>361</v>
       </c>
       <c r="E284" s="3"/>
-      <c r="F284" s="3"/>
-      <c r="G284" s="3"/>
+      <c r="F284" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="G284" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H284" s="3"/>
       <c r="I284" s="3" t="s">
         <v>58</v>
@@ -43910,8 +46004,12 @@
         <v>361</v>
       </c>
       <c r="E285" s="3"/>
-      <c r="F285" s="3"/>
-      <c r="G285" s="3"/>
+      <c r="F285" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="G285" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H285" s="3"/>
       <c r="I285" s="3" t="s">
         <v>58</v>
@@ -43931,8 +46029,12 @@
         <v>362</v>
       </c>
       <c r="E286" s="3"/>
-      <c r="F286" s="3"/>
-      <c r="G286" s="3"/>
+      <c r="F286" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="G286" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="H286" s="3"/>
       <c r="I286" s="3" t="s">
         <v>58</v>
@@ -43952,8 +46054,12 @@
         <v>364</v>
       </c>
       <c r="E287" s="3"/>
-      <c r="F287" s="3"/>
-      <c r="G287" s="3"/>
+      <c r="F287" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="G287" s="3" t="s">
+        <v>1011</v>
+      </c>
       <c r="H287" s="3"/>
       <c r="I287" s="3" t="s">
         <v>58</v>
@@ -43973,8 +46079,12 @@
         <v>361</v>
       </c>
       <c r="E288" s="3"/>
-      <c r="F288" s="3"/>
-      <c r="G288" s="3"/>
+      <c r="F288" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="G288" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H288" s="3"/>
       <c r="I288" s="3" t="s">
         <v>58</v>
@@ -43994,8 +46104,12 @@
         <v>361</v>
       </c>
       <c r="E289" s="3"/>
-      <c r="F289" s="3"/>
-      <c r="G289" s="3"/>
+      <c r="F289" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="G289" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H289" s="3"/>
       <c r="I289" s="3" t="s">
         <v>58</v>
@@ -44015,8 +46129,12 @@
         <v>361</v>
       </c>
       <c r="E290" s="3"/>
-      <c r="F290" s="3"/>
-      <c r="G290" s="3"/>
+      <c r="F290" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="G290" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="H290" s="3"/>
       <c r="I290" s="3" t="s">
         <v>58</v>
@@ -44036,8 +46154,12 @@
         <v>70</v>
       </c>
       <c r="E291" s="3"/>
-      <c r="F291" s="3"/>
-      <c r="G291" s="3"/>
+      <c r="F291" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="G291" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H291" s="3"/>
       <c r="I291" s="3" t="s">
         <v>58</v>
@@ -44057,8 +46179,12 @@
         <v>70</v>
       </c>
       <c r="E292" s="3"/>
-      <c r="F292" s="3"/>
-      <c r="G292" s="3"/>
+      <c r="F292" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="G292" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H292" s="3"/>
       <c r="I292" s="3" t="s">
         <v>58</v>
@@ -44078,8 +46204,12 @@
         <v>70</v>
       </c>
       <c r="E293" s="3"/>
-      <c r="F293" s="3"/>
-      <c r="G293" s="3"/>
+      <c r="F293" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="G293" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H293" s="3"/>
       <c r="I293" s="3" t="s">
         <v>58</v>
@@ -44099,8 +46229,12 @@
         <v>70</v>
       </c>
       <c r="E294" s="3"/>
-      <c r="F294" s="3"/>
-      <c r="G294" s="3"/>
+      <c r="F294" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="G294" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H294" s="3"/>
       <c r="I294" s="3" t="s">
         <v>58</v>
@@ -44120,8 +46254,12 @@
         <v>70</v>
       </c>
       <c r="E295" s="3"/>
-      <c r="F295" s="3"/>
-      <c r="G295" s="3"/>
+      <c r="F295" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="G295" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H295" s="3"/>
       <c r="I295" s="3" t="s">
         <v>58</v>
@@ -44141,8 +46279,12 @@
         <v>70</v>
       </c>
       <c r="E296" s="3"/>
-      <c r="F296" s="3"/>
-      <c r="G296" s="3"/>
+      <c r="F296" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="G296" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H296" s="3"/>
       <c r="I296" s="3" t="s">
         <v>58</v>
@@ -44162,8 +46304,12 @@
         <v>70</v>
       </c>
       <c r="E297" s="3"/>
-      <c r="F297" s="3"/>
-      <c r="G297" s="3"/>
+      <c r="F297" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="G297" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H297" s="3"/>
       <c r="I297" s="3" t="s">
         <v>58</v>
@@ -44183,8 +46329,12 @@
         <v>70</v>
       </c>
       <c r="E298" s="3"/>
-      <c r="F298" s="3"/>
-      <c r="G298" s="3"/>
+      <c r="F298" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="G298" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H298" s="3"/>
       <c r="I298" s="3" t="s">
         <v>58</v>
@@ -44204,8 +46354,12 @@
         <v>70</v>
       </c>
       <c r="E299" s="3"/>
-      <c r="F299" s="3"/>
-      <c r="G299" s="3"/>
+      <c r="F299" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="G299" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H299" s="3"/>
       <c r="I299" s="3" t="s">
         <v>58</v>
@@ -44225,8 +46379,12 @@
         <v>70</v>
       </c>
       <c r="E300" s="3"/>
-      <c r="F300" s="3"/>
-      <c r="G300" s="3"/>
+      <c r="F300" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="G300" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H300" s="3"/>
       <c r="I300" s="3" t="s">
         <v>58</v>
@@ -44246,8 +46404,12 @@
         <v>70</v>
       </c>
       <c r="E301" s="3"/>
-      <c r="F301" s="3"/>
-      <c r="G301" s="3"/>
+      <c r="F301" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="G301" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H301" s="3"/>
       <c r="I301" s="3" t="s">
         <v>58</v>
@@ -44267,8 +46429,12 @@
         <v>70</v>
       </c>
       <c r="E302" s="3"/>
-      <c r="F302" s="3"/>
-      <c r="G302" s="3"/>
+      <c r="F302" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="G302" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H302" s="3"/>
       <c r="I302" s="3" t="s">
         <v>58</v>
@@ -44288,8 +46454,12 @@
         <v>70</v>
       </c>
       <c r="E303" s="3"/>
-      <c r="F303" s="3"/>
-      <c r="G303" s="3"/>
+      <c r="F303" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G303" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H303" s="3"/>
       <c r="I303" s="3" t="s">
         <v>58</v>
@@ -44309,8 +46479,12 @@
         <v>70</v>
       </c>
       <c r="E304" s="3"/>
-      <c r="F304" s="3"/>
-      <c r="G304" s="3"/>
+      <c r="F304" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G304" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H304" s="3"/>
       <c r="I304" s="3" t="s">
         <v>58</v>
@@ -44330,8 +46504,12 @@
         <v>70</v>
       </c>
       <c r="E305" s="3"/>
-      <c r="F305" s="3"/>
-      <c r="G305" s="3"/>
+      <c r="F305" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G305" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H305" s="3"/>
       <c r="I305" s="3" t="s">
         <v>58</v>
@@ -44351,8 +46529,12 @@
         <v>70</v>
       </c>
       <c r="E306" s="3"/>
-      <c r="F306" s="3"/>
-      <c r="G306" s="3"/>
+      <c r="F306" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G306" s="3" t="s">
+        <v>1005</v>
+      </c>
       <c r="H306" s="3"/>
       <c r="I306" s="3" t="s">
         <v>58</v>
@@ -49098,7 +51280,7 @@
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>696</v>
+        <v>1016</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>372</v>
@@ -49112,7 +51294,7 @@
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>696</v>
+        <v>1016</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>372</v>
@@ -49126,7 +51308,7 @@
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>696</v>
+        <v>1016</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>372</v>
@@ -49140,7 +51322,7 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>696</v>
+        <v>1016</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>372</v>
@@ -49154,7 +51336,7 @@
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>696</v>
+        <v>1016</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>372</v>
@@ -49169,7 +51351,7 @@
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>696</v>
+        <v>1016</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>372</v>
@@ -49183,7 +51365,7 @@
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>696</v>
+        <v>1016</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>372</v>
